--- a/results/tscv/consolidated/NF_vs_Standard_GARCH_Comparison.xlsx
+++ b/results/tscv/consolidated/NF_vs_Standard_GARCH_Comparison.xlsx
@@ -36,37 +36,37 @@
     <t xml:space="preserve">Overall mean MSE - Standard</t>
   </si>
   <si>
-    <t xml:space="preserve">0.000388013175393389</t>
+    <t xml:space="preserve">0.000360394077523137</t>
   </si>
   <si>
     <t xml:space="preserve">Overall mean MSE - NF-GARCH</t>
   </si>
   <si>
-    <t xml:space="preserve">0.00114457744000315</t>
+    <t xml:space="preserve">0.000370066981776579</t>
   </si>
   <si>
     <t xml:space="preserve">Overall mean AIC - Standard</t>
   </si>
   <si>
-    <t xml:space="preserve">-15940.078354814</t>
+    <t xml:space="preserve">-17086.4328956155</t>
   </si>
   <si>
     <t xml:space="preserve">Overall mean AIC - NF-GARCH</t>
   </si>
   <si>
-    <t xml:space="preserve">-14677.019841565</t>
+    <t xml:space="preserve">-16430.0131017179</t>
   </si>
   <si>
     <t xml:space="preserve">NF-GARCH wins (lower MSE)</t>
   </si>
   <si>
-    <t xml:space="preserve">4</t>
+    <t xml:space="preserve">5</t>
   </si>
   <si>
     <t xml:space="preserve">Standard GARCH wins (lower MSE)</t>
   </si>
   <si>
-    <t xml:space="preserve">2</t>
+    <t xml:space="preserve">1</t>
   </si>
   <si>
     <t xml:space="preserve">Overall winner</t>
@@ -728,23 +728,23 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>-11646.7464398731</v>
+        <v>-17419.3665038942</v>
       </c>
       <c r="E2"/>
       <c r="F2" t="n">
-        <v>-11616.8258300795</v>
+        <v>-17389.4458941006</v>
       </c>
       <c r="G2"/>
       <c r="H2" t="n">
-        <v>0.0027011384354426</v>
+        <v>0.000355295536092039</v>
       </c>
       <c r="I2"/>
       <c r="J2" t="n">
-        <v>0.0357135766317098</v>
+        <v>0.0115514657708642</v>
       </c>
       <c r="K2"/>
       <c r="L2" t="n">
-        <v>5828.37321993652</v>
+        <v>8714.68325194709</v>
       </c>
       <c r="M2"/>
       <c r="N2"/>
@@ -763,23 +763,23 @@
       </c>
       <c r="D3"/>
       <c r="E3" t="n">
-        <v>-16492.244919545</v>
+        <v>-17855.0642576084</v>
       </c>
       <c r="F3"/>
       <c r="G3" t="n">
-        <v>-16456.3401877928</v>
+        <v>-17819.1595258562</v>
       </c>
       <c r="H3"/>
       <c r="I3" t="n">
-        <v>0.00037461225810351</v>
+        <v>0.000355448286815202</v>
       </c>
       <c r="J3"/>
       <c r="K3" t="n">
-        <v>0.0119614251372998</v>
+        <v>0.0115241200592389</v>
       </c>
       <c r="L3"/>
       <c r="M3" t="n">
-        <v>8252.12245977249</v>
+        <v>8933.53212880421</v>
       </c>
       <c r="N3"/>
       <c r="O3"/>
@@ -790,65 +790,65 @@
         <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
-      <c r="D4"/>
-      <c r="E4" t="n">
-        <v>635.787255489474</v>
-      </c>
-      <c r="F4"/>
-      <c r="G4" t="n">
-        <v>671.691987241692</v>
-      </c>
-      <c r="H4"/>
-      <c r="I4" t="n">
-        <v>0.000903033428318554</v>
-      </c>
-      <c r="J4"/>
-      <c r="K4" t="n">
-        <v>0.0226485436100141</v>
-      </c>
-      <c r="L4"/>
-      <c r="M4" t="n">
-        <v>-311.893627744737</v>
-      </c>
+      <c r="D4" t="n">
+        <v>-13348.1714003446</v>
+      </c>
+      <c r="E4"/>
+      <c r="F4" t="n">
+        <v>-13318.2507905511</v>
+      </c>
+      <c r="G4"/>
+      <c r="H4" t="n">
+        <v>0.000500426622455502</v>
+      </c>
+      <c r="I4"/>
+      <c r="J4" t="n">
+        <v>0.0158945008810578</v>
+      </c>
+      <c r="K4"/>
+      <c r="L4" t="n">
+        <v>6679.08570017231</v>
+      </c>
+      <c r="M4"/>
       <c r="N4"/>
       <c r="O4"/>
       <c r="P4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
-      <c r="D5" t="n">
-        <v>-17046.7988844799</v>
-      </c>
-      <c r="E5"/>
-      <c r="F5" t="n">
-        <v>-17016.8782746864</v>
-      </c>
-      <c r="G5"/>
-      <c r="H5" t="n">
-        <v>0.000361200918683921</v>
-      </c>
-      <c r="I5"/>
-      <c r="J5" t="n">
-        <v>0.0116155234628555</v>
-      </c>
-      <c r="K5"/>
-      <c r="L5" t="n">
-        <v>8528.39944223996</v>
-      </c>
-      <c r="M5"/>
+      <c r="D5"/>
+      <c r="E5" t="n">
+        <v>-17546.387452374</v>
+      </c>
+      <c r="F5"/>
+      <c r="G5" t="n">
+        <v>-17510.4827206217</v>
+      </c>
+      <c r="H5"/>
+      <c r="I5" t="n">
+        <v>0.000355420109113578</v>
+      </c>
+      <c r="J5"/>
+      <c r="K5" t="n">
+        <v>0.0115128911580025</v>
+      </c>
+      <c r="L5"/>
+      <c r="M5" t="n">
+        <v>8779.19372618698</v>
+      </c>
       <c r="N5"/>
       <c r="O5"/>
       <c r="P5"/>
@@ -858,118 +858,152 @@
         <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
-      <c r="D6"/>
-      <c r="E6" t="n">
-        <v>-17512.3222721118</v>
-      </c>
-      <c r="F6"/>
-      <c r="G6" t="n">
-        <v>-17476.4175403596</v>
-      </c>
-      <c r="H6"/>
-      <c r="I6" t="n">
-        <v>0.000358082572078918</v>
-      </c>
-      <c r="J6"/>
-      <c r="K6" t="n">
-        <v>0.0115700437788557</v>
-      </c>
-      <c r="L6"/>
-      <c r="M6" t="n">
-        <v>8762.16113605591</v>
-      </c>
+      <c r="D6" t="n">
+        <v>-17046.7988844799</v>
+      </c>
+      <c r="E6"/>
+      <c r="F6" t="n">
+        <v>-17016.8782746864</v>
+      </c>
+      <c r="G6"/>
+      <c r="H6" t="n">
+        <v>0.000361785836574961</v>
+      </c>
+      <c r="I6"/>
+      <c r="J6" t="n">
+        <v>0.0115903677737828</v>
+      </c>
+      <c r="K6"/>
+      <c r="L6" t="n">
+        <v>8528.39944223996</v>
+      </c>
+      <c r="M6"/>
       <c r="N6"/>
       <c r="O6"/>
       <c r="P6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" t="n">
-        <v>-15337.514200342</v>
-      </c>
+      <c r="D7"/>
       <c r="E7" t="n">
-        <v>-15337.514200342</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-15313.5777125072</v>
-      </c>
+        <v>-17512.3222721118</v>
+      </c>
+      <c r="F7"/>
       <c r="G7" t="n">
-        <v>-15313.5777125072</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.000371392965882915</v>
-      </c>
+        <v>-17476.4175403596</v>
+      </c>
+      <c r="H7"/>
       <c r="I7" t="n">
-        <v>0.000369997511829952</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.0118306849563225</v>
-      </c>
+        <v>0.000357995410498175</v>
+      </c>
+      <c r="J7"/>
       <c r="K7" t="n">
-        <v>0.0119135805219756</v>
-      </c>
-      <c r="L7" t="n">
-        <v>7672.757100171</v>
-      </c>
+        <v>0.0115758689500471</v>
+      </c>
+      <c r="L7"/>
       <c r="M7" t="n">
-        <v>7672.75710017099</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.00000000000909494701772928</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-0.377152280311727</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.69580732257793</v>
-      </c>
+        <v>8762.16113605591</v>
+      </c>
+      <c r="N7"/>
+      <c r="O7"/>
+      <c r="P7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
-      <c r="D8"/>
+      <c r="D8" t="n">
+        <v>-15337.514200342</v>
+      </c>
       <c r="E8" t="n">
+        <v>-15337.514200342</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-15313.5777125072</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-15313.5777125072</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.000371392965882915</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.000370538839829169</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0118306849563225</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0119233586315027</v>
+      </c>
+      <c r="L8" t="n">
+        <v>7672.757100171</v>
+      </c>
+      <c r="M8" t="n">
+        <v>7672.75710017099</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.00000000000909494701772928</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.230509183366683</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.777244718072311</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9"/>
+      <c r="E9" t="n">
         <v>-17180.8762956412</v>
       </c>
-      <c r="F8"/>
-      <c r="G8" t="n">
+      <c r="F9"/>
+      <c r="G9" t="n">
         <v>-17150.9556858477</v>
       </c>
-      <c r="H8"/>
-      <c r="I8" t="n">
-        <v>0.000363523650740316</v>
-      </c>
-      <c r="J8"/>
-      <c r="K8" t="n">
-        <v>0.0116832206076774</v>
-      </c>
-      <c r="L8"/>
-      <c r="M8" t="n">
+      <c r="H9"/>
+      <c r="I9" t="n">
+        <v>0.000362567741359561</v>
+      </c>
+      <c r="J9"/>
+      <c r="K9" t="n">
+        <v>0.0116821611811747</v>
+      </c>
+      <c r="L9"/>
+      <c r="M9" t="n">
         <v>8595.43814782061</v>
       </c>
-      <c r="N8"/>
-      <c r="O8"/>
-      <c r="P8"/>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1004,16 +1038,16 @@
         <v>45</v>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>-14677.019841565</v>
+        <v>-16430.0131017179</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00114457744000315</v>
+        <v>0.000370066981776579</v>
       </c>
       <c r="E2" t="n">
-        <v>0.019719928350296</v>
+        <v>0.0118805058887829</v>
       </c>
     </row>
     <row r="3">
@@ -1021,16 +1055,16 @@
         <v>46</v>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C3" t="n">
-        <v>-15940.078354814</v>
+        <v>-17086.4328956155</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000388013175393389</v>
+        <v>0.000360394077523137</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0122167265553946</v>
+        <v>0.0116436799959932</v>
       </c>
     </row>
   </sheetData>
@@ -1072,10 +1106,10 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>66.6666666666667</v>
+        <v>83.3333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -1205,7 +1239,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
         <v>36</v>
@@ -1214,22 +1248,22 @@
         <v>59</v>
       </c>
       <c r="D4" t="n">
-        <v>-11957.8877932379</v>
+        <v>-12886.6841895632</v>
       </c>
       <c r="E4" t="n">
-        <v>-11921.9830614857</v>
+        <v>-12850.779457811</v>
       </c>
       <c r="F4" t="n">
-        <v>5984.94389661896</v>
+        <v>6449.34209478161</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00117495727203218</v>
+        <v>0.00111555473489436</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0253258713658253</v>
+        <v>0.0243001914052754</v>
       </c>
       <c r="I4" t="n">
-        <v>2695.60599869737</v>
+        <v>3132.11008984489</v>
       </c>
       <c r="J4" t="n">
         <v>200</v>
@@ -1243,7 +1277,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
         <v>36</v>
@@ -1252,22 +1286,22 @@
         <v>59</v>
       </c>
       <c r="D5" t="n">
-        <v>-13272.5886735945</v>
+        <v>-13301.5420123857</v>
       </c>
       <c r="E5" t="n">
-        <v>-13236.6839418423</v>
+        <v>-13265.6372806335</v>
       </c>
       <c r="F5" t="n">
-        <v>6642.29433679725</v>
+        <v>6656.77100619286</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00112104391654069</v>
+        <v>0.00111670795691699</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0244353868579965</v>
+        <v>0.024358729224578</v>
       </c>
       <c r="I5" t="n">
-        <v>3072.1587297151</v>
+        <v>3042.68454556731</v>
       </c>
       <c r="J5" t="n">
         <v>200</v>
@@ -1281,31 +1315,31 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D6" t="n">
-        <v>-13915.8189354138</v>
+        <v>-13272.5886735945</v>
       </c>
       <c r="E6" t="n">
-        <v>-13891.882447579</v>
+        <v>-13236.6839418423</v>
       </c>
       <c r="F6" t="n">
-        <v>6961.90946770692</v>
+        <v>6642.29433679725</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000360304448428351</v>
+        <v>0.00112497443727646</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0134165504693556</v>
+        <v>0.024469170371814</v>
       </c>
       <c r="I6" t="n">
-        <v>4016.03855790491</v>
+        <v>3030.709446039</v>
       </c>
       <c r="J6" t="n">
         <v>200</v>
@@ -1322,28 +1356,28 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
         <v>61</v>
       </c>
       <c r="D7" t="n">
-        <v>-16187.7828771156</v>
+        <v>-13915.8189354138</v>
       </c>
       <c r="E7" t="n">
-        <v>-16157.8622673221</v>
+        <v>-13891.882447579</v>
       </c>
       <c r="F7" t="n">
-        <v>8098.89143855781</v>
+        <v>6961.90946770692</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000359628582719831</v>
+        <v>0.000361254926614895</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01337808460704</v>
+        <v>0.0134550585967499</v>
       </c>
       <c r="I7" t="n">
-        <v>3989.26065346736</v>
+        <v>4023.62831318396</v>
       </c>
       <c r="J7" t="n">
         <v>200</v>
@@ -1357,7 +1391,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
         <v>36</v>
@@ -1366,22 +1400,22 @@
         <v>61</v>
       </c>
       <c r="D8" t="n">
-        <v>-15439.990288026</v>
+        <v>-16187.7828771156</v>
       </c>
       <c r="E8" t="n">
-        <v>-15404.0855562738</v>
+        <v>-16157.8622673221</v>
       </c>
       <c r="F8" t="n">
-        <v>7725.99514401299</v>
+        <v>8098.89143855781</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000361364401060953</v>
+        <v>0.000361466683062339</v>
       </c>
       <c r="H8" t="n">
-        <v>0.013410208563299</v>
+        <v>0.0134273038980847</v>
       </c>
       <c r="I8" t="n">
-        <v>3059.08434608172</v>
+        <v>4043.21255953561</v>
       </c>
       <c r="J8" t="n">
         <v>200</v>
@@ -1395,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
         <v>36</v>
@@ -1404,22 +1438,22 @@
         <v>61</v>
       </c>
       <c r="D9" t="n">
-        <v>-16714.5673553433</v>
+        <v>-16459.2335450459</v>
       </c>
       <c r="E9" t="n">
-        <v>-16678.6626235911</v>
+        <v>-16423.3288132937</v>
       </c>
       <c r="F9" t="n">
-        <v>8363.28367767167</v>
+        <v>8235.61677252294</v>
       </c>
       <c r="G9" t="n">
-        <v>0.000359777178385612</v>
+        <v>0.000359999596247787</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0133598521697371</v>
+        <v>0.0133725240496058</v>
       </c>
       <c r="I9" t="n">
-        <v>4037.26469185038</v>
+        <v>4065.87000184499</v>
       </c>
       <c r="J9" t="n">
         <v>200</v>
@@ -1433,31 +1467,31 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D10" t="n">
-        <v>-11081.523323752</v>
+        <v>-16755.7121347858</v>
       </c>
       <c r="E10" t="n">
-        <v>-11057.5868359172</v>
+        <v>-16719.8074030336</v>
       </c>
       <c r="F10" t="n">
-        <v>5544.76166187601</v>
+        <v>8383.85606739289</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00056346552788844</v>
+        <v>0.000358760404644373</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0175136645335045</v>
+        <v>0.0133665089714111</v>
       </c>
       <c r="I10" t="n">
-        <v>3687.39504638638</v>
+        <v>3993.2608258732</v>
       </c>
       <c r="J10" t="n">
         <v>200</v>
@@ -1471,31 +1505,31 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" t="s">
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D11" t="n">
-        <v>-13905.261927556</v>
+        <v>-16714.5673553433</v>
       </c>
       <c r="E11" t="n">
-        <v>-13875.3413177625</v>
+        <v>-16678.6626235911</v>
       </c>
       <c r="F11" t="n">
-        <v>6957.63096377799</v>
+        <v>8363.28367767167</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00052106886525686</v>
+        <v>0.000356743550893258</v>
       </c>
       <c r="H11" t="n">
-        <v>0.016373736181268</v>
+        <v>0.0133016781178622</v>
       </c>
       <c r="I11" t="n">
-        <v>3703.40076560579</v>
+        <v>3977.8279110375</v>
       </c>
       <c r="J11" t="n">
         <v>200</v>
@@ -1509,31 +1543,31 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
         <v>62</v>
       </c>
       <c r="D12" t="n">
-        <v>635.787255489474</v>
+        <v>-11081.523323752</v>
       </c>
       <c r="E12" t="n">
-        <v>671.691987241692</v>
+        <v>-11057.5868359172</v>
       </c>
       <c r="F12" t="n">
-        <v>-311.893627744737</v>
+        <v>5544.76166187601</v>
       </c>
       <c r="G12" t="n">
-        <v>0.000903033428318554</v>
+        <v>0.000564922744948614</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0226485436100141</v>
+        <v>0.0174227356790865</v>
       </c>
       <c r="I12" t="n">
-        <v>3442.55343250256</v>
+        <v>3688.95048356413</v>
       </c>
       <c r="J12" t="n">
         <v>200</v>
@@ -1547,7 +1581,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
         <v>36</v>
@@ -1556,22 +1590,22 @@
         <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>-13205.7862971612</v>
+        <v>-13905.261927556</v>
       </c>
       <c r="E13" t="n">
-        <v>-13169.881565409</v>
+        <v>-13875.3413177625</v>
       </c>
       <c r="F13" t="n">
-        <v>6608.89314858061</v>
+        <v>6957.63096377799</v>
       </c>
       <c r="G13" t="n">
-        <v>0.000552026351989601</v>
+        <v>0.00051256253852644</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0172299819605147</v>
+        <v>0.0162964583934212</v>
       </c>
       <c r="I13" t="n">
-        <v>3443.47726359418</v>
+        <v>3726.29492781905</v>
       </c>
       <c r="J13" t="n">
         <v>200</v>
@@ -1585,7 +1619,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
         <v>36</v>
@@ -1594,22 +1628,22 @@
         <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>-14011.7133296657</v>
+        <v>-14264.3558075108</v>
       </c>
       <c r="E14" t="n">
-        <v>-13975.8085979135</v>
+        <v>-14228.4510757586</v>
       </c>
       <c r="F14" t="n">
-        <v>7011.85666483284</v>
+        <v>7138.17790375541</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000510589415988203</v>
+        <v>0.000500949612146857</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0160588342085541</v>
+        <v>0.0158879486872876</v>
       </c>
       <c r="I14" t="n">
-        <v>3733.47728974512</v>
+        <v>3813.08701133096</v>
       </c>
       <c r="J14" t="n">
         <v>200</v>
@@ -1623,31 +1657,31 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>-19372.7663740109</v>
+        <v>-14556.4722711371</v>
       </c>
       <c r="E15" t="n">
-        <v>-19348.829886176</v>
+        <v>-14520.5675393849</v>
       </c>
       <c r="F15" t="n">
-        <v>9690.38318700543</v>
+        <v>7284.23613556855</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0000231098553213341</v>
+        <v>0.000501761655645969</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00359934063113566</v>
+        <v>0.0159259194630122</v>
       </c>
       <c r="I15" t="n">
-        <v>5999.96106229826</v>
+        <v>3782.81897948546</v>
       </c>
       <c r="J15" t="n">
         <v>200</v>
@@ -1656,36 +1690,36 @@
         <v>46</v>
       </c>
       <c r="L15" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>-21086.222814587</v>
+        <v>-14011.7133296657</v>
       </c>
       <c r="E16" t="n">
-        <v>-21056.3022047935</v>
+        <v>-13975.8085979135</v>
       </c>
       <c r="F16" t="n">
-        <v>10548.1114072935</v>
+        <v>7011.85666483284</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0000232056291139487</v>
+        <v>0.000510320566076767</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00360873445507718</v>
+        <v>0.0161365366418438</v>
       </c>
       <c r="I16" t="n">
-        <v>5992.66029045404</v>
+        <v>3767.62074431485</v>
       </c>
       <c r="J16" t="n">
         <v>200</v>
@@ -1694,36 +1728,36 @@
         <v>46</v>
       </c>
       <c r="L16" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
         <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>-20390.7246340714</v>
+        <v>-19372.7663740109</v>
       </c>
       <c r="E17" t="n">
-        <v>-20354.8199023192</v>
+        <v>-19348.829886176</v>
       </c>
       <c r="F17" t="n">
-        <v>10201.3623170357</v>
+        <v>9690.38318700543</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0000241413063637064</v>
+        <v>0.0000236414128735109</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00368673516890196</v>
+        <v>0.0036471405536792</v>
       </c>
       <c r="I17" t="n">
-        <v>5467.67308986778</v>
+        <v>5987.28183715359</v>
       </c>
       <c r="J17" t="n">
         <v>200</v>
@@ -1737,7 +1771,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
@@ -1746,22 +1780,22 @@
         <v>63</v>
       </c>
       <c r="D18" t="n">
-        <v>-21219.4284734558</v>
+        <v>-21086.222814587</v>
       </c>
       <c r="E18" t="n">
-        <v>-21183.5237417036</v>
+        <v>-21056.3022047935</v>
       </c>
       <c r="F18" t="n">
-        <v>10615.7142367279</v>
+        <v>10548.1114072935</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0000228134861742642</v>
+        <v>0.0000231225271578479</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00356119558849934</v>
+        <v>0.00359127607084575</v>
       </c>
       <c r="I18" t="n">
-        <v>6042.55013502725</v>
+        <v>5994.51025599374</v>
       </c>
       <c r="J18" t="n">
         <v>200</v>
@@ -1775,31 +1809,31 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D19" t="n">
-        <v>-20093.9832449172</v>
+        <v>-21640.2971385716</v>
       </c>
       <c r="E19" t="n">
-        <v>-20070.0467570823</v>
+        <v>-21604.3924068193</v>
       </c>
       <c r="F19" t="n">
-        <v>10050.9916224586</v>
+        <v>10826.1485692858</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0000349732866618819</v>
+        <v>0.0000222439071814552</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00438900250787526</v>
+        <v>0.00352767472559489</v>
       </c>
       <c r="I19" t="n">
-        <v>5786.11570119715</v>
+        <v>6158.51780261829</v>
       </c>
       <c r="J19" t="n">
         <v>200</v>
@@ -1813,31 +1847,31 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
         <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D20" t="n">
-        <v>-21446.4359075332</v>
+        <v>-21907.805785593</v>
       </c>
       <c r="E20" t="n">
-        <v>-21416.5152977397</v>
+        <v>-21871.9010538407</v>
       </c>
       <c r="F20" t="n">
-        <v>10728.2179537666</v>
+        <v>10959.9028927965</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0000344380230880276</v>
+        <v>0.0000218834164508473</v>
       </c>
       <c r="H20" t="n">
-        <v>0.00434630303947548</v>
+        <v>0.00348439023508079</v>
       </c>
       <c r="I20" t="n">
-        <v>5780.09352947</v>
+        <v>6196.70043012867</v>
       </c>
       <c r="J20" t="n">
         <v>200</v>
@@ -1851,31 +1885,31 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s">
         <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D21" t="n">
-        <v>-20663.0629217926</v>
+        <v>-21219.4284734558</v>
       </c>
       <c r="E21" t="n">
-        <v>-20627.1581900404</v>
+        <v>-21183.5237417036</v>
       </c>
       <c r="F21" t="n">
-        <v>10337.5314608963</v>
+        <v>10615.7142367279</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0000357988619098349</v>
+        <v>0.0000229634382419525</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00444410511997457</v>
+        <v>0.00357748912445529</v>
       </c>
       <c r="I21" t="n">
-        <v>5080.54587866973</v>
+        <v>6053.09816335699</v>
       </c>
       <c r="J21" t="n">
         <v>200</v>
@@ -1889,31 +1923,31 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
         <v>65</v>
       </c>
       <c r="D22" t="n">
-        <v>-21922.1562477529</v>
+        <v>-20093.9832449172</v>
       </c>
       <c r="E22" t="n">
-        <v>-21886.2515160007</v>
+        <v>-20070.0467570823</v>
       </c>
       <c r="F22" t="n">
-        <v>10967.0781238764</v>
+        <v>10050.9916224586</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0000344570297091276</v>
+        <v>0.0000351113442536926</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00432648013859719</v>
+        <v>0.00439870385864537</v>
       </c>
       <c r="I22" t="n">
-        <v>5887.50065183515</v>
+        <v>5774.19764879581</v>
       </c>
       <c r="J22" t="n">
         <v>200</v>
@@ -1930,28 +1964,28 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D23" t="n">
-        <v>-16711.3634303374</v>
+        <v>-21446.4359075332</v>
       </c>
       <c r="E23" t="n">
-        <v>-16687.4269425026</v>
+        <v>-21416.5152977397</v>
       </c>
       <c r="F23" t="n">
-        <v>8359.6817151687</v>
+        <v>10728.2179537666</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0000997222522262377</v>
+        <v>0.0000351150224151743</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00767446897223286</v>
+        <v>0.00439406088023143</v>
       </c>
       <c r="I23" t="n">
-        <v>4898.76289219843</v>
+        <v>5780.09321421133</v>
       </c>
       <c r="J23" t="n">
         <v>200</v>
@@ -1965,31 +1999,31 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B24" t="s">
         <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D24" t="n">
-        <v>-17841.2674418593</v>
+        <v>-21775.2300244312</v>
       </c>
       <c r="E24" t="n">
-        <v>-17811.3468320658</v>
+        <v>-21739.325292679</v>
       </c>
       <c r="F24" t="n">
-        <v>8925.63372092964</v>
+        <v>10893.6150122156</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0000990080817025684</v>
+        <v>0.0000345009050030342</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00768860348015291</v>
+        <v>0.00431691918580554</v>
       </c>
       <c r="I24" t="n">
-        <v>4911.44624946992</v>
+        <v>5882.13461935128</v>
       </c>
       <c r="J24" t="n">
         <v>200</v>
@@ -2009,25 +2043,25 @@
         <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D25" t="n">
-        <v>-17296.0175829807</v>
+        <v>-22143.852773775</v>
       </c>
       <c r="E25" t="n">
-        <v>-17260.1128512285</v>
+        <v>-22107.9480420228</v>
       </c>
       <c r="F25" t="n">
-        <v>8654.00879149036</v>
+        <v>11077.9263868875</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0000993853552647834</v>
+        <v>0.0000346127833191152</v>
       </c>
       <c r="H25" t="n">
-        <v>0.00767164864528331</v>
+        <v>0.00433154931649469</v>
       </c>
       <c r="I25" t="n">
-        <v>4170.05463873219</v>
+        <v>5886.36568963006</v>
       </c>
       <c r="J25" t="n">
         <v>200</v>
@@ -2047,25 +2081,25 @@
         <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D26" t="n">
-        <v>-17933.4795528587</v>
+        <v>-21922.1562477529</v>
       </c>
       <c r="E26" t="n">
-        <v>-17897.5748211065</v>
+        <v>-21886.2515160007</v>
       </c>
       <c r="F26" t="n">
-        <v>8972.73977642934</v>
+        <v>10967.0781238764</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0000998144056756081</v>
+        <v>0.0000344783826509954</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00767851370975007</v>
+        <v>0.00432326276233044</v>
       </c>
       <c r="I26" t="n">
-        <v>4961.98613255461</v>
+        <v>5890.9308124457</v>
       </c>
       <c r="J26" t="n">
         <v>200</v>
@@ -2085,31 +2119,31 @@
         <v>35</v>
       </c>
       <c r="C27" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D27" t="n">
-        <v>-19372.7663740109</v>
+        <v>-16711.3634303374</v>
       </c>
       <c r="E27" t="n">
-        <v>-19348.829886176</v>
+        <v>-16687.4269425026</v>
       </c>
       <c r="F27" t="n">
-        <v>9690.38318700543</v>
+        <v>8359.6817151687</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0000221746894915632</v>
+        <v>0.0000998929098308323</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00350321108239467</v>
+        <v>0.00772805708310525</v>
       </c>
       <c r="I27" t="n">
-        <v>6014.83158238363</v>
+        <v>4908.13119999712</v>
       </c>
       <c r="J27" t="n">
         <v>200</v>
       </c>
       <c r="K27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L27" t="s">
         <v>64</v>
@@ -2120,34 +2154,34 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D28" t="n">
-        <v>-20093.9832449172</v>
+        <v>-17841.2674418593</v>
       </c>
       <c r="E28" t="n">
-        <v>-20070.0467570823</v>
+        <v>-17811.3468320658</v>
       </c>
       <c r="F28" t="n">
-        <v>10050.9916224586</v>
+        <v>8925.63372092964</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0000342260571424258</v>
+        <v>0.0000993469544349091</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00430731155749105</v>
+        <v>0.00768000596141435</v>
       </c>
       <c r="I28" t="n">
-        <v>5476.6380116998</v>
+        <v>4924.38827164208</v>
       </c>
       <c r="J28" t="n">
         <v>200</v>
       </c>
       <c r="K28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L28" t="s">
         <v>64</v>
@@ -2155,37 +2189,37 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" t="s">
         <v>66</v>
       </c>
       <c r="D29" t="n">
-        <v>-16711.3634303374</v>
+        <v>-18252.5240091211</v>
       </c>
       <c r="E29" t="n">
-        <v>-16687.4269425026</v>
+        <v>-18216.6192773689</v>
       </c>
       <c r="F29" t="n">
-        <v>8359.6817151687</v>
+        <v>9132.26200456054</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0000982743675609389</v>
+        <v>0.0000992718992079738</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00768679788169922</v>
+        <v>0.00767208889444575</v>
       </c>
       <c r="I29" t="n">
-        <v>4469.35178960953</v>
+        <v>5040.13702461136</v>
       </c>
       <c r="J29" t="n">
         <v>200</v>
       </c>
       <c r="K29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L29" t="s">
         <v>64</v>
@@ -2193,78 +2227,78 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C30" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D30" t="n">
-        <v>-10849.6298936207</v>
+        <v>-18465.0005679739</v>
       </c>
       <c r="E30" t="n">
-        <v>-10825.6934057859</v>
+        <v>-18429.0958362217</v>
       </c>
       <c r="F30" t="n">
-        <v>5428.81494681033</v>
+        <v>9238.50028398695</v>
       </c>
       <c r="G30" t="n">
-        <v>0.00112840091247088</v>
+        <v>0.0000989635039139146</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0243402449940381</v>
+        <v>0.00767762314485683</v>
       </c>
       <c r="I30" t="n">
-        <v>2205.49063288371</v>
+        <v>5009.62614301722</v>
       </c>
       <c r="J30" t="n">
         <v>200</v>
       </c>
       <c r="K30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L30" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C31" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D31" t="n">
-        <v>-13915.8189354138</v>
+        <v>-17933.4795528587</v>
       </c>
       <c r="E31" t="n">
-        <v>-13891.882447579</v>
+        <v>-17897.5748211065</v>
       </c>
       <c r="F31" t="n">
-        <v>6961.90946770692</v>
+        <v>8972.73977642934</v>
       </c>
       <c r="G31" t="n">
-        <v>0.000381090090987412</v>
+        <v>0.0000984920878496141</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0138581890523909</v>
+        <v>0.0076470766819771</v>
       </c>
       <c r="I31" t="n">
-        <v>3183.70218896155</v>
+        <v>4943.99795678676</v>
       </c>
       <c r="J31" t="n">
         <v>200</v>
       </c>
       <c r="K31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L31" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32">
@@ -2275,25 +2309,25 @@
         <v>35</v>
       </c>
       <c r="C32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D32" t="n">
-        <v>-11081.523323752</v>
+        <v>-19372.7663740109</v>
       </c>
       <c r="E32" t="n">
-        <v>-11057.5868359172</v>
+        <v>-19348.829886176</v>
       </c>
       <c r="F32" t="n">
-        <v>5544.76166187601</v>
+        <v>9690.38318700543</v>
       </c>
       <c r="G32" t="n">
-        <v>0.000564191677644273</v>
+        <v>0.0000221746894915632</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0172883551699212</v>
+        <v>0.00350321108239467</v>
       </c>
       <c r="I32" t="n">
-        <v>3204.5048231739</v>
+        <v>6014.83158238363</v>
       </c>
       <c r="J32" t="n">
         <v>200</v>
@@ -2302,36 +2336,36 @@
         <v>45</v>
       </c>
       <c r="L32" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B33" t="s">
         <v>35</v>
       </c>
       <c r="C33" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D33" t="n">
-        <v>-21449.8072377658</v>
+        <v>-20093.9832449172</v>
       </c>
       <c r="E33" t="n">
-        <v>-21419.8866279722</v>
+        <v>-20070.0467570823</v>
       </c>
       <c r="F33" t="n">
-        <v>10729.9036188829</v>
+        <v>10050.9916224586</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0000221882886681815</v>
+        <v>0.0000342260571424258</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00351650605743122</v>
+        <v>0.00430731155749105</v>
       </c>
       <c r="I33" t="n">
-        <v>6152.30003709659</v>
+        <v>5476.6380116998</v>
       </c>
       <c r="J33" t="n">
         <v>200</v>
@@ -2345,31 +2379,31 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B34" t="s">
         <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D34" t="n">
-        <v>-20490.9474569145</v>
+        <v>-16711.3634303374</v>
       </c>
       <c r="E34" t="n">
-        <v>-20461.026847121</v>
+        <v>-16687.4269425026</v>
       </c>
       <c r="F34" t="n">
-        <v>10250.4737284573</v>
+        <v>8359.6817151687</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0000344188241789488</v>
+        <v>0.0000982743675609389</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00431407435634202</v>
+        <v>0.00768679788169922</v>
       </c>
       <c r="I34" t="n">
-        <v>5686.45364640743</v>
+        <v>4469.35178960953</v>
       </c>
       <c r="J34" t="n">
         <v>200</v>
@@ -2383,31 +2417,31 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B35" t="s">
         <v>35</v>
       </c>
       <c r="C35" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D35" t="n">
-        <v>-18400.8070339588</v>
+        <v>-10849.6298936207</v>
       </c>
       <c r="E35" t="n">
-        <v>-18370.8864241653</v>
+        <v>-10825.6934057859</v>
       </c>
       <c r="F35" t="n">
-        <v>9205.40351697942</v>
+        <v>5428.81494681033</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0000984362686406674</v>
+        <v>0.00112840091247088</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00763607955202054</v>
+        <v>0.0243402449940381</v>
       </c>
       <c r="I35" t="n">
-        <v>4997.07461126552</v>
+        <v>2205.49063288371</v>
       </c>
       <c r="J35" t="n">
         <v>200</v>
@@ -2416,36 +2450,36 @@
         <v>45</v>
       </c>
       <c r="L35" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="s">
         <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D36" t="n">
-        <v>-12539.2488040093</v>
+        <v>-13915.8189354138</v>
       </c>
       <c r="E36" t="n">
-        <v>-12509.3281942158</v>
+        <v>-13891.882447579</v>
       </c>
       <c r="F36" t="n">
-        <v>6274.62440200463</v>
+        <v>6961.90946770692</v>
       </c>
       <c r="G36" t="n">
-        <v>0.00114451904023182</v>
+        <v>0.000381090090987412</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0247522442410187</v>
+        <v>0.0138581890523909</v>
       </c>
       <c r="I36" t="n">
-        <v>2662.72659174263</v>
+        <v>3183.70218896155</v>
       </c>
       <c r="J36" t="n">
         <v>200</v>
@@ -2459,31 +2493,31 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37" t="s">
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D37" t="n">
-        <v>-16142.3583943172</v>
+        <v>-11081.523323752</v>
       </c>
       <c r="E37" t="n">
-        <v>-16112.4377845237</v>
+        <v>-11057.5868359172</v>
       </c>
       <c r="F37" t="n">
-        <v>8076.17919715859</v>
+        <v>5544.76166187601</v>
       </c>
       <c r="G37" t="n">
-        <v>0.000358693818621905</v>
+        <v>0.000564191677644273</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0133645491847223</v>
+        <v>0.0172883551699212</v>
       </c>
       <c r="I37" t="n">
-        <v>4076.43048758304</v>
+        <v>3204.5048231739</v>
       </c>
       <c r="J37" t="n">
         <v>200</v>
@@ -2497,7 +2531,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" t="s">
         <v>35</v>
@@ -2506,22 +2540,22 @@
         <v>62</v>
       </c>
       <c r="D38" t="n">
-        <v>-13257.6243799139</v>
+        <v>-13348.1714003446</v>
       </c>
       <c r="E38" t="n">
-        <v>-13227.7037701204</v>
+        <v>-13318.2507905511</v>
       </c>
       <c r="F38" t="n">
-        <v>6633.81218995694</v>
+        <v>6679.08570017231</v>
       </c>
       <c r="G38" t="n">
-        <v>0.000508949271762003</v>
+        <v>0.000500426622455502</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0161096873855982</v>
+        <v>0.0158945008810578</v>
       </c>
       <c r="I38" t="n">
-        <v>3634.73892595781</v>
+        <v>3739.77278199111</v>
       </c>
       <c r="J38" t="n">
         <v>200</v>
@@ -2535,7 +2569,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B39" t="s">
         <v>35</v>
@@ -2544,22 +2578,22 @@
         <v>63</v>
       </c>
       <c r="D39" t="n">
-        <v>-17061.4856551161</v>
+        <v>-21449.8072377658</v>
       </c>
       <c r="E39" t="n">
-        <v>-17031.5650453226</v>
+        <v>-21419.8866279722</v>
       </c>
       <c r="F39" t="n">
-        <v>8535.74282755804</v>
+        <v>10729.9036188829</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0000620396788378124</v>
+        <v>0.0000221376007540136</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00677446044422478</v>
+        <v>0.00349886759169113</v>
       </c>
       <c r="I39" t="n">
-        <v>1249.8098993698</v>
+        <v>6159.92584093635</v>
       </c>
       <c r="J39" t="n">
         <v>200</v>
@@ -2573,7 +2607,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
         <v>35</v>
@@ -2582,22 +2616,22 @@
         <v>65</v>
       </c>
       <c r="D40" t="n">
-        <v>-17182.902204236</v>
+        <v>-20490.9474569145</v>
       </c>
       <c r="E40" t="n">
-        <v>-17152.9815944425</v>
+        <v>-20461.026847121</v>
       </c>
       <c r="F40" t="n">
-        <v>8596.45110211799</v>
+        <v>10250.4737284573</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0000463950155142026</v>
+        <v>0.0000343006214269721</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00524001079364371</v>
+        <v>0.00431339941862002</v>
       </c>
       <c r="I40" t="n">
-        <v>1231.22524913944</v>
+        <v>5687.06929887019</v>
       </c>
       <c r="J40" t="n">
         <v>200</v>
@@ -2611,7 +2645,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B41" t="s">
         <v>35</v>
@@ -2620,22 +2654,22 @@
         <v>66</v>
       </c>
       <c r="D41" t="n">
-        <v>-14859.4187816532</v>
+        <v>-18400.8070339588</v>
       </c>
       <c r="E41" t="n">
-        <v>-14829.4981718597</v>
+        <v>-18370.8864241653</v>
       </c>
       <c r="F41" t="n">
-        <v>7434.7093908266</v>
+        <v>9205.40351697942</v>
       </c>
       <c r="G41" t="n">
-        <v>0.000104407593001443</v>
+        <v>0.0000987341385758633</v>
       </c>
       <c r="H41" t="n">
-        <v>0.00799406496794956</v>
+        <v>0.00768155294121907</v>
       </c>
       <c r="I41" t="n">
-        <v>-291.487300846552</v>
+        <v>4999.34986165365</v>
       </c>
       <c r="J41" t="n">
         <v>200</v>
@@ -2649,7 +2683,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B42" t="s">
         <v>35</v>
@@ -2658,22 +2692,22 @@
         <v>59</v>
       </c>
       <c r="D42" t="n">
-        <v>-8645.20114912874</v>
+        <v>-12539.2488040093</v>
       </c>
       <c r="E42" t="n">
-        <v>-8615.28053933522</v>
+        <v>-12509.3281942158</v>
       </c>
       <c r="F42" t="n">
-        <v>4327.60057456437</v>
+        <v>6274.62440200463</v>
       </c>
       <c r="G42" t="n">
-        <v>0.00162425634969949</v>
+        <v>0.00114716275172289</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0311635106215592</v>
+        <v>0.0246198141599958</v>
       </c>
       <c r="I42" t="n">
-        <v>-3302.59065779187</v>
+        <v>2668.16263062273</v>
       </c>
       <c r="J42" t="n">
         <v>200</v>
@@ -2687,7 +2721,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B43" t="s">
         <v>35</v>
@@ -2696,22 +2730,22 @@
         <v>61</v>
       </c>
       <c r="D43" t="n">
-        <v>-6873.88504119932</v>
+        <v>-16142.3583943172</v>
       </c>
       <c r="E43" t="n">
-        <v>-6843.96443140581</v>
+        <v>-16112.4377845237</v>
       </c>
       <c r="F43" t="n">
-        <v>3441.94252059966</v>
+        <v>8076.17919715859</v>
       </c>
       <c r="G43" t="n">
-        <v>0.00529963962488016</v>
+        <v>0.000360553162906069</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0704208080729092</v>
+        <v>0.0133867662019792</v>
       </c>
       <c r="I43" t="n">
-        <v>-1786.7704898554</v>
+        <v>4068.71442510312</v>
       </c>
       <c r="J43" t="n">
         <v>200</v>
@@ -2725,7 +2759,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B44" t="s">
         <v>35</v>
@@ -2734,22 +2768,22 @@
         <v>62</v>
       </c>
       <c r="D44" t="n">
-        <v>-5257.58580790495</v>
+        <v>-13257.6243799139</v>
       </c>
       <c r="E44" t="n">
-        <v>-5227.66519811144</v>
+        <v>-13227.7037701204</v>
       </c>
       <c r="F44" t="n">
-        <v>2633.79290395248</v>
+        <v>6633.81218995694</v>
       </c>
       <c r="G44" t="n">
-        <v>0.00907009235072251</v>
+        <v>0.000507826744063959</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0926886048899726</v>
+        <v>0.0160418063291914</v>
       </c>
       <c r="I44" t="n">
-        <v>-3209.56148929613</v>
+        <v>3605.56296403186</v>
       </c>
       <c r="J44" t="n">
         <v>200</v>
@@ -2758,6 +2792,234 @@
         <v>45</v>
       </c>
       <c r="L44" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" t="s">
+        <v>35</v>
+      </c>
+      <c r="C45" t="s">
+        <v>63</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-21603.960640254</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-21574.0400304605</v>
+      </c>
+      <c r="F45" t="n">
+        <v>10806.980320127</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.0000239608723647867</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.00373800491196438</v>
+      </c>
+      <c r="I45" t="n">
+        <v>4687.19660993523</v>
+      </c>
+      <c r="J45" t="n">
+        <v>200</v>
+      </c>
+      <c r="K45" t="s">
+        <v>45</v>
+      </c>
+      <c r="L45" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" t="s">
+        <v>35</v>
+      </c>
+      <c r="C46" t="s">
+        <v>65</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-21950.5756080947</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-21920.6549983012</v>
+      </c>
+      <c r="F46" t="n">
+        <v>10980.2878040474</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.0000348715203082612</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.00434793195857652</v>
+      </c>
+      <c r="I46" t="n">
+        <v>5680.1669551618</v>
+      </c>
+      <c r="J46" t="n">
+        <v>200</v>
+      </c>
+      <c r="K46" t="s">
+        <v>45</v>
+      </c>
+      <c r="L46" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>34</v>
+      </c>
+      <c r="B47" t="s">
+        <v>35</v>
+      </c>
+      <c r="C47" t="s">
+        <v>66</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-18443.7255754793</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-18413.8049656858</v>
+      </c>
+      <c r="F47" t="n">
+        <v>9226.86278773967</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.0000985096363115153</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.00765192479069071</v>
+      </c>
+      <c r="I47" t="n">
+        <v>4993.47994505337</v>
+      </c>
+      <c r="J47" t="n">
+        <v>200</v>
+      </c>
+      <c r="K47" t="s">
+        <v>45</v>
+      </c>
+      <c r="L47" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>34</v>
+      </c>
+      <c r="B48" t="s">
+        <v>35</v>
+      </c>
+      <c r="C48" t="s">
+        <v>59</v>
+      </c>
+      <c r="D48" t="n">
+        <v>-12745.1907692674</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-12715.2701594739</v>
+      </c>
+      <c r="F48" t="n">
+        <v>6377.59538463372</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.00111955844457315</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.0243926830197835</v>
+      </c>
+      <c r="I48" t="n">
+        <v>3114.93991550959</v>
+      </c>
+      <c r="J48" t="n">
+        <v>200</v>
+      </c>
+      <c r="K48" t="s">
+        <v>45</v>
+      </c>
+      <c r="L48" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49" t="s">
+        <v>61</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-16194.7563532163</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-16164.8357434228</v>
+      </c>
+      <c r="F49" t="n">
+        <v>8102.37817660814</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.00035948830300169</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.013377217032468</v>
+      </c>
+      <c r="I49" t="n">
+        <v>4053.15633503966</v>
+      </c>
+      <c r="J49" t="n">
+        <v>200</v>
+      </c>
+      <c r="K49" t="s">
+        <v>45</v>
+      </c>
+      <c r="L49" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" t="s">
+        <v>35</v>
+      </c>
+      <c r="C50" t="s">
+        <v>62</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-13577.9900770532</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-13548.0694672597</v>
+      </c>
+      <c r="F50" t="n">
+        <v>6793.9950385266</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.000495384439992828</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.015801032911702</v>
+      </c>
+      <c r="I50" t="n">
+        <v>3586.41769262345</v>
+      </c>
+      <c r="J50" t="n">
+        <v>200</v>
+      </c>
+      <c r="K50" t="s">
+        <v>45</v>
+      </c>
+      <c r="L50" t="s">
         <v>60</v>
       </c>
     </row>
@@ -2806,10 +3068,10 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
@@ -2869,22 +3131,22 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00223109257078005</v>
+        <v>0.000656408314981865</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00112840091247088</v>
+        <v>0.00050412668325973</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0337762437346812</v>
+        <v>0.0179000609752528</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0243402449940381</v>
+        <v>0.0159681536051246</v>
       </c>
       <c r="H2" t="n">
-        <v>-10951.4306365844</v>
+        <v>-13365.2312330908</v>
       </c>
       <c r="I2" t="n">
-        <v>-11081.523323752</v>
+        <v>-13302.8978901293</v>
       </c>
     </row>
     <row r="3">
@@ -2898,22 +3160,22 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000697650908586416</v>
+        <v>0.000668545455393949</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000552026351989601</v>
+        <v>0.000510320566076767</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0186725409559931</v>
+        <v>0.0180875387600556</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0172299819605147</v>
+        <v>0.0161365366418438</v>
       </c>
       <c r="H3" t="n">
-        <v>-12501.926941861</v>
+        <v>-14052.0782054458</v>
       </c>
       <c r="I3" t="n">
-        <v>-13272.5886735945</v>
+        <v>-13915.8189354138</v>
       </c>
     </row>
     <row r="4">
@@ -2927,22 +3189,22 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0000580623092262426</v>
+        <v>0.0000519099448818156</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0000463950155142026</v>
+        <v>0.0000343006214269721</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00566361296591075</v>
+        <v>0.00519211134826075</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00524001079364371</v>
+        <v>0.00431339941862002</v>
       </c>
       <c r="H4" t="n">
-        <v>-18402.6090465455</v>
+        <v>-19835.3262890814</v>
       </c>
       <c r="I4" t="n">
-        <v>-18400.8070339588</v>
+        <v>-20093.9832449172</v>
       </c>
     </row>
     <row r="5">
@@ -2956,22 +3218,22 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0000525722977676102</v>
+        <v>0.0000522426996523246</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0000347151581855047</v>
+        <v>0.0000346127833191152</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00522292762141298</v>
+        <v>0.00519982123193084</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00436765277367537</v>
+        <v>0.00433154931649469</v>
       </c>
       <c r="H5" t="n">
-        <v>-19664.7423855131</v>
+        <v>-20120.7875857852</v>
       </c>
       <c r="I5" t="n">
-        <v>-20242.3539394943</v>
+        <v>-21086.222814587</v>
       </c>
     </row>
   </sheetData>
@@ -3004,26 +3266,40 @@
         <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B3" t="s">
         <v>46</v>
       </c>
       <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>66.6666666666667</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
         <v>100</v>
       </c>
     </row>

--- a/results/tscv/consolidated/NF_vs_Standard_GARCH_Comparison.xlsx
+++ b/results/tscv/consolidated/NF_vs_Standard_GARCH_Comparison.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
   <si>
     <t xml:space="preserve">Question</t>
   </si>
@@ -36,37 +36,37 @@
     <t xml:space="preserve">Overall mean MSE - Standard</t>
   </si>
   <si>
-    <t xml:space="preserve">0.000360394077523137</t>
+    <t xml:space="preserve">0.000354709318762894</t>
   </si>
   <si>
     <t xml:space="preserve">Overall mean MSE - NF-GARCH</t>
   </si>
   <si>
-    <t xml:space="preserve">0.000370066981776579</t>
+    <t xml:space="preserve">0.000430403906144569</t>
   </si>
   <si>
     <t xml:space="preserve">Overall mean AIC - Standard</t>
   </si>
   <si>
-    <t xml:space="preserve">-17086.4328956155</t>
+    <t xml:space="preserve">-17662.5142560387</t>
   </si>
   <si>
     <t xml:space="preserve">Overall mean AIC - NF-GARCH</t>
   </si>
   <si>
-    <t xml:space="preserve">-16430.0131017179</t>
+    <t xml:space="preserve">-17147.8374747076</t>
   </si>
   <si>
     <t xml:space="preserve">NF-GARCH wins (lower MSE)</t>
   </si>
   <si>
-    <t xml:space="preserve">5</t>
+    <t xml:space="preserve">6</t>
   </si>
   <si>
     <t xml:space="preserve">Standard GARCH wins (lower MSE)</t>
   </si>
   <si>
-    <t xml:space="preserve">1</t>
+    <t xml:space="preserve">12</t>
   </si>
   <si>
     <t xml:space="preserve">Overall winner</t>
@@ -124,9 +124,6 @@
   </si>
   <si>
     <t xml:space="preserve">TGARCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">norm</t>
   </si>
   <si>
     <t xml:space="preserve">std</t>
@@ -728,62 +725,94 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>-17419.3665038942</v>
-      </c>
-      <c r="E2"/>
+        <v>-17855.0642576084</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-17855.0642576084</v>
+      </c>
       <c r="F2" t="n">
-        <v>-17389.4458941006</v>
-      </c>
-      <c r="G2"/>
+        <v>-17819.1595258562</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-17819.1595258562</v>
+      </c>
       <c r="H2" t="n">
-        <v>0.000355295536092039</v>
-      </c>
-      <c r="I2"/>
+        <v>0.000354812739410202</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.000354083088947051</v>
+      </c>
       <c r="J2" t="n">
-        <v>0.0115514657708642</v>
-      </c>
-      <c r="K2"/>
+        <v>0.0114907861087824</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0114868949753609</v>
+      </c>
       <c r="L2" t="n">
-        <v>8714.68325194709</v>
-      </c>
-      <c r="M2"/>
-      <c r="N2"/>
-      <c r="O2"/>
-      <c r="P2"/>
+        <v>8933.53212880421</v>
+      </c>
+      <c r="M2" t="n">
+        <v>8933.53212880421</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.00000000000363797880709171</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.206067582984568</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.0338745451215462</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
-      <c r="D3"/>
+      <c r="D3" t="n">
+        <v>-17546.387452374</v>
+      </c>
       <c r="E3" t="n">
-        <v>-17855.0642576084</v>
-      </c>
-      <c r="F3"/>
+        <v>-17546.387452374</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-17510.4827206218</v>
+      </c>
       <c r="G3" t="n">
-        <v>-17819.1595258562</v>
-      </c>
-      <c r="H3"/>
+        <v>-17510.4827206217</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.000355981298891738</v>
+      </c>
       <c r="I3" t="n">
-        <v>0.000355448286815202</v>
-      </c>
-      <c r="J3"/>
+        <v>0.000355303039142247</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.0115224438911848</v>
+      </c>
       <c r="K3" t="n">
-        <v>0.0115241200592389</v>
-      </c>
-      <c r="L3"/>
+        <v>0.0115272723594018</v>
+      </c>
+      <c r="L3" t="n">
+        <v>8779.19372618698</v>
+      </c>
       <c r="M3" t="n">
-        <v>8933.53212880421</v>
-      </c>
-      <c r="N3"/>
-      <c r="O3"/>
-      <c r="P3"/>
+        <v>8779.19372618698</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.00000000000727595761418343</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-0.190896129436118</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.0418873439125912</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
@@ -793,26 +822,26 @@
         <v>35</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>-13348.1714003446</v>
+        <v>-17303.1040922302</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="n">
-        <v>-13318.2507905511</v>
+        <v>-17267.199360478</v>
       </c>
       <c r="G4"/>
       <c r="H4" t="n">
-        <v>0.000500426622455502</v>
+        <v>0.000502923399449053</v>
       </c>
       <c r="I4"/>
       <c r="J4" t="n">
-        <v>0.0158945008810578</v>
+        <v>0.0140006563624044</v>
       </c>
       <c r="K4"/>
       <c r="L4" t="n">
-        <v>6679.08570017231</v>
+        <v>8657.55204611511</v>
       </c>
       <c r="M4"/>
       <c r="N4"/>
@@ -824,30 +853,30 @@
         <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5"/>
       <c r="E5" t="n">
-        <v>-17546.387452374</v>
+        <v>-17512.3222721118</v>
       </c>
       <c r="F5"/>
       <c r="G5" t="n">
-        <v>-17510.4827206217</v>
+        <v>-17476.4175403596</v>
       </c>
       <c r="H5"/>
       <c r="I5" t="n">
-        <v>0.000355420109113578</v>
+        <v>0.000354766034996837</v>
       </c>
       <c r="J5"/>
       <c r="K5" t="n">
-        <v>0.0115128911580025</v>
+        <v>0.0115046808319871</v>
       </c>
       <c r="L5"/>
       <c r="M5" t="n">
-        <v>8779.19372618698</v>
+        <v>8762.16113605591</v>
       </c>
       <c r="N5"/>
       <c r="O5"/>
@@ -861,26 +890,26 @@
         <v>35</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>-17046.7988844799</v>
+        <v>-14781.0173360503</v>
       </c>
       <c r="E6"/>
       <c r="F6" t="n">
-        <v>-17016.8782746864</v>
+        <v>-14751.0967262568</v>
       </c>
       <c r="G6"/>
       <c r="H6" t="n">
-        <v>0.000361785836574961</v>
+        <v>0.000657911960814483</v>
       </c>
       <c r="I6"/>
       <c r="J6" t="n">
-        <v>0.0115903677737828</v>
+        <v>0.0178496205551987</v>
       </c>
       <c r="K6"/>
       <c r="L6" t="n">
-        <v>8528.39944223996</v>
+        <v>7395.50866802516</v>
       </c>
       <c r="M6"/>
       <c r="N6"/>
@@ -892,118 +921,34 @@
         <v>38</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7"/>
       <c r="E7" t="n">
-        <v>-17512.3222721118</v>
+        <v>-17736.2830420607</v>
       </c>
       <c r="F7"/>
       <c r="G7" t="n">
-        <v>-17476.4175403596</v>
+        <v>-17706.3624322672</v>
       </c>
       <c r="H7"/>
       <c r="I7" t="n">
-        <v>0.000357995410498175</v>
+        <v>0.000354685111965443</v>
       </c>
       <c r="J7"/>
       <c r="K7" t="n">
-        <v>0.0115758689500471</v>
+        <v>0.0114940875284057</v>
       </c>
       <c r="L7"/>
       <c r="M7" t="n">
-        <v>8762.16113605591</v>
+        <v>8873.14152103034</v>
       </c>
       <c r="N7"/>
       <c r="O7"/>
       <c r="P7"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-15337.514200342</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-15337.514200342</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-15313.5777125072</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-15313.5777125072</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.000371392965882915</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.000370538839829169</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.0118306849563225</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.0119233586315027</v>
-      </c>
-      <c r="L8" t="n">
-        <v>7672.757100171</v>
-      </c>
-      <c r="M8" t="n">
-        <v>7672.75710017099</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.00000000000909494701772928</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-0.230509183366683</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.777244718072311</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9"/>
-      <c r="E9" t="n">
-        <v>-17180.8762956412</v>
-      </c>
-      <c r="F9"/>
-      <c r="G9" t="n">
-        <v>-17150.9556858477</v>
-      </c>
-      <c r="H9"/>
-      <c r="I9" t="n">
-        <v>0.000362567741359561</v>
-      </c>
-      <c r="J9"/>
-      <c r="K9" t="n">
-        <v>0.0116821611811747</v>
-      </c>
-      <c r="L9"/>
-      <c r="M9" t="n">
-        <v>8595.43814782061</v>
-      </c>
-      <c r="N9"/>
-      <c r="O9"/>
-      <c r="P9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1018,53 +963,53 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" t="s">
         <v>40</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>41</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>42</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>43</v>
-      </c>
-      <c r="E1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>-16430.0131017179</v>
+        <v>-17147.8374747076</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000370066981776579</v>
+        <v>0.000430403906144569</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0118805058887829</v>
+        <v>0.0129794561529229</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>-17086.4328956155</v>
+        <v>-17662.5142560387</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000360394077523137</v>
+        <v>0.000354709318762894</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0116436799959932</v>
+        <v>0.0115032339237889</v>
       </c>
     </row>
   </sheetData>
@@ -1086,18 +1031,18 @@
         <v>19</v>
       </c>
       <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" t="s">
         <v>47</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>48</v>
-      </c>
-      <c r="E1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
         <v>35</v>
@@ -1106,10 +1051,61 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>83.3333333333333</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>33.3333333333333</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>66.6666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1131,186 +1127,186 @@
         <v>19</v>
       </c>
       <c r="C1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" t="s">
         <v>50</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>51</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>52</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>53</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>54</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>55</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>56</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" t="s">
         <v>57</v>
-      </c>
-      <c r="K1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
         <v>35</v>
       </c>
       <c r="C2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-13207.8962469027</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-13177.9756371092</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6608.94812345134</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.00111851385672083</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.0243253412648991</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1038.84151555585</v>
+      </c>
+      <c r="J2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L2" t="s">
         <v>59</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-10849.6298936207</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-10825.6934057859</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5428.81494681033</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.00113840970045347</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.02488845601775</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3063.75616843326</v>
-      </c>
-      <c r="J2" t="n">
-        <v>200</v>
-      </c>
-      <c r="K2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L2" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-12886.6841895632</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-12850.779457811</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6449.34209478161</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.00111692540425677</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0243272587456195</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2713.56426922374</v>
+      </c>
+      <c r="J3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L3" t="s">
         <v>59</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-12618.2868051962</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-12588.3661954027</v>
-      </c>
-      <c r="F3" t="n">
-        <v>6314.14340259809</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.00114379272256066</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.0247038618830511</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3040.61592704401</v>
-      </c>
-      <c r="J3" t="n">
-        <v>200</v>
-      </c>
-      <c r="K3" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-13301.5420123857</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-13265.6372806335</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6656.77100619286</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0011149496035565</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.024286042178787</v>
+      </c>
+      <c r="I4" t="n">
+        <v>785.377293173349</v>
+      </c>
+      <c r="J4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K4" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" t="s">
         <v>59</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-12886.6841895632</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-12850.779457811</v>
-      </c>
-      <c r="F4" t="n">
-        <v>6449.34209478161</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.00111555473489436</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0243001914052754</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3132.11008984489</v>
-      </c>
-      <c r="J4" t="n">
-        <v>200</v>
-      </c>
-      <c r="K4" t="s">
-        <v>46</v>
-      </c>
-      <c r="L4" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-13272.5886735945</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-13236.6839418423</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6642.29433679725</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.00111569642979297</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0243177177264599</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-659.934951682068</v>
+      </c>
+      <c r="J5" t="n">
+        <v>100</v>
+      </c>
+      <c r="K5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L5" t="s">
         <v>59</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-13301.5420123857</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-13265.6372806335</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6656.77100619286</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.00111670795691699</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.024358729224578</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3042.68454556731</v>
-      </c>
-      <c r="J5" t="n">
-        <v>200</v>
-      </c>
-      <c r="K5" t="s">
-        <v>46</v>
-      </c>
-      <c r="L5" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="6">
@@ -1318,113 +1314,113 @@
         <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-16688.7587376761</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-16658.8381278826</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8349.37936883806</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.000357500435245033</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0133096618481464</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2704.26626555954</v>
+      </c>
+      <c r="J6" t="n">
+        <v>100</v>
+      </c>
+      <c r="K6" t="s">
+        <v>45</v>
+      </c>
+      <c r="L6" t="s">
         <v>59</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-13272.5886735945</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-13236.6839418423</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6642.29433679725</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.00112497443727646</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.024469170371814</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3030.709446039</v>
-      </c>
-      <c r="J6" t="n">
-        <v>200</v>
-      </c>
-      <c r="K6" t="s">
-        <v>46</v>
-      </c>
-      <c r="L6" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
         <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D7" t="n">
-        <v>-13915.8189354138</v>
+        <v>-16459.2335450459</v>
       </c>
       <c r="E7" t="n">
-        <v>-13891.882447579</v>
+        <v>-16423.3288132937</v>
       </c>
       <c r="F7" t="n">
-        <v>6961.90946770692</v>
+        <v>8235.61677252294</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000361254926614895</v>
+        <v>0.000359105140455086</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0134550585967499</v>
+        <v>0.0133380761670115</v>
       </c>
       <c r="I7" t="n">
-        <v>4023.62831318396</v>
+        <v>3569.07229575078</v>
       </c>
       <c r="J7" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D8" t="n">
-        <v>-16187.7828771156</v>
+        <v>-16755.7121347858</v>
       </c>
       <c r="E8" t="n">
-        <v>-16157.8622673221</v>
+        <v>-16719.8074030336</v>
       </c>
       <c r="F8" t="n">
-        <v>8098.89143855781</v>
+        <v>8383.85606739289</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000361466683062339</v>
+        <v>0.000357616757349892</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0134273038980847</v>
+        <v>0.013324888440816</v>
       </c>
       <c r="I8" t="n">
-        <v>4043.21255953561</v>
+        <v>2443.02408491458</v>
       </c>
       <c r="J8" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
@@ -1432,417 +1428,417 @@
         <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D9" t="n">
-        <v>-16459.2335450459</v>
+        <v>-16714.5673553433</v>
       </c>
       <c r="E9" t="n">
-        <v>-16423.3288132937</v>
+        <v>-16678.6626235911</v>
       </c>
       <c r="F9" t="n">
-        <v>8235.61677252294</v>
+        <v>8363.28367767167</v>
       </c>
       <c r="G9" t="n">
-        <v>0.000359999596247787</v>
+        <v>0.000356632504957771</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0133725240496058</v>
+        <v>0.0133146730085331</v>
       </c>
       <c r="I9" t="n">
-        <v>4065.87000184499</v>
+        <v>3129.02754930411</v>
       </c>
       <c r="J9" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
         <v>61</v>
       </c>
       <c r="D10" t="n">
-        <v>-16755.7121347858</v>
+        <v>-14446.3970235722</v>
       </c>
       <c r="E10" t="n">
-        <v>-16719.8074030336</v>
+        <v>-14416.4764137787</v>
       </c>
       <c r="F10" t="n">
-        <v>8383.85606739289</v>
+        <v>7228.19851178609</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000358760404644373</v>
+        <v>0.000497147014810391</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0133665089714111</v>
+        <v>0.0158477359464996</v>
       </c>
       <c r="I10" t="n">
-        <v>3993.2608258732</v>
+        <v>2859.0613648566</v>
       </c>
       <c r="J10" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
         <v>61</v>
       </c>
       <c r="D11" t="n">
-        <v>-16714.5673553433</v>
+        <v>-14264.3558075108</v>
       </c>
       <c r="E11" t="n">
-        <v>-16678.6626235911</v>
+        <v>-14228.4510757586</v>
       </c>
       <c r="F11" t="n">
-        <v>8363.28367767167</v>
+        <v>7138.17790375541</v>
       </c>
       <c r="G11" t="n">
-        <v>0.000356743550893258</v>
+        <v>0.000500250823983806</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0133016781178622</v>
+        <v>0.0159769806422821</v>
       </c>
       <c r="I11" t="n">
-        <v>3977.8279110375</v>
+        <v>3622.5691129771</v>
       </c>
       <c r="J11" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>-11081.523323752</v>
+        <v>-14556.4722711371</v>
       </c>
       <c r="E12" t="n">
-        <v>-11057.5868359172</v>
+        <v>-14520.5675393849</v>
       </c>
       <c r="F12" t="n">
-        <v>5544.76166187601</v>
+        <v>7284.23613556855</v>
       </c>
       <c r="G12" t="n">
-        <v>0.000564922744948614</v>
+        <v>0.000497233192647025</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0174227356790865</v>
+        <v>0.0158559419937669</v>
       </c>
       <c r="I12" t="n">
-        <v>3688.95048356413</v>
+        <v>2346.57626978034</v>
       </c>
       <c r="J12" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>-13905.261927556</v>
+        <v>-14011.7133296657</v>
       </c>
       <c r="E13" t="n">
-        <v>-13875.3413177625</v>
+        <v>-13975.8085979135</v>
       </c>
       <c r="F13" t="n">
-        <v>6957.63096377799</v>
+        <v>7011.85666483284</v>
       </c>
       <c r="G13" t="n">
-        <v>0.00051256253852644</v>
+        <v>0.000501215976354351</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0162964583934212</v>
+        <v>0.0159017915906153</v>
       </c>
       <c r="I13" t="n">
-        <v>3726.29492781905</v>
+        <v>3386.24190851075</v>
       </c>
       <c r="J13" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
         <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>-14264.3558075108</v>
+        <v>-21728.6026698585</v>
       </c>
       <c r="E14" t="n">
-        <v>-14228.4510757586</v>
+        <v>-21698.682060065</v>
       </c>
       <c r="F14" t="n">
-        <v>7138.17790375541</v>
+        <v>10869.3013349292</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000500949612146857</v>
+        <v>0.0000223627813478594</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0158879486872876</v>
+        <v>0.00353359621682163</v>
       </c>
       <c r="I14" t="n">
-        <v>3813.08701133096</v>
+        <v>6037.12475217081</v>
       </c>
       <c r="J14" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L14" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
         <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>-14556.4722711371</v>
+        <v>-21640.2971385716</v>
       </c>
       <c r="E15" t="n">
-        <v>-14520.5675393849</v>
+        <v>-21604.3924068193</v>
       </c>
       <c r="F15" t="n">
-        <v>7284.23613556855</v>
+        <v>10826.1485692858</v>
       </c>
       <c r="G15" t="n">
-        <v>0.000501761655645969</v>
+        <v>0.0000223129991188355</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0159259194630122</v>
+        <v>0.00352247019300576</v>
       </c>
       <c r="I15" t="n">
-        <v>3782.81897948546</v>
+        <v>6204.93485317718</v>
       </c>
       <c r="J15" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L15" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
         <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>-14011.7133296657</v>
+        <v>-21907.805785593</v>
       </c>
       <c r="E16" t="n">
-        <v>-13975.8085979135</v>
+        <v>-21871.9010538407</v>
       </c>
       <c r="F16" t="n">
-        <v>7011.85666483284</v>
+        <v>10959.9028927965</v>
       </c>
       <c r="G16" t="n">
-        <v>0.000510320566076767</v>
+        <v>0.000022227606782021</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0161365366418438</v>
+        <v>0.00351111212333665</v>
       </c>
       <c r="I16" t="n">
-        <v>3767.62074431485</v>
+        <v>5760.26085402423</v>
       </c>
       <c r="J16" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L16" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
       <c r="C17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-21219.4284734558</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-21183.5237417036</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10615.7142367279</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.000022136450465134</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.00350657493240071</v>
+      </c>
+      <c r="I17" t="n">
+        <v>6022.36885159423</v>
+      </c>
+      <c r="J17" t="n">
+        <v>100</v>
+      </c>
+      <c r="K17" t="s">
+        <v>45</v>
+      </c>
+      <c r="L17" t="s">
         <v>63</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-19372.7663740109</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-19348.829886176</v>
-      </c>
-      <c r="F17" t="n">
-        <v>9690.38318700543</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.0000236414128735109</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.0036471405536792</v>
-      </c>
-      <c r="I17" t="n">
-        <v>5987.28183715359</v>
-      </c>
-      <c r="J17" t="n">
-        <v>200</v>
-      </c>
-      <c r="K17" t="s">
-        <v>46</v>
-      </c>
-      <c r="L17" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-22032.0789112467</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-22002.1583014532</v>
+      </c>
+      <c r="F18" t="n">
+        <v>11021.0394556234</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.0000343920616004835</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.00432101987130455</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5056.18016341248</v>
+      </c>
+      <c r="J18" t="n">
+        <v>100</v>
+      </c>
+      <c r="K18" t="s">
+        <v>45</v>
+      </c>
+      <c r="L18" t="s">
         <v>63</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-21086.222814587</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-21056.3022047935</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10548.1114072935</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.0000231225271578479</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.00359127607084575</v>
-      </c>
-      <c r="I18" t="n">
-        <v>5994.51025599374</v>
-      </c>
-      <c r="J18" t="n">
-        <v>200</v>
-      </c>
-      <c r="K18" t="s">
-        <v>46</v>
-      </c>
-      <c r="L18" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-21775.2300244312</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-21739.325292679</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10893.6150122156</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0000344259538106167</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.00433438276462643</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5715.1088056586</v>
+      </c>
+      <c r="J19" t="n">
+        <v>100</v>
+      </c>
+      <c r="K19" t="s">
+        <v>45</v>
+      </c>
+      <c r="L19" t="s">
         <v>63</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-21640.2971385716</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-21604.3924068193</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10826.1485692858</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.0000222439071814552</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.00352767472559489</v>
-      </c>
-      <c r="I19" t="n">
-        <v>6158.51780261829</v>
-      </c>
-      <c r="J19" t="n">
-        <v>200</v>
-      </c>
-      <c r="K19" t="s">
-        <v>46</v>
-      </c>
-      <c r="L19" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -1850,80 +1846,80 @@
         <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-22143.852773775</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-22107.9480420228</v>
+      </c>
+      <c r="F20" t="n">
+        <v>11077.9263868875</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.0000344510416572018</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.00432715118307698</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5065.35447795538</v>
+      </c>
+      <c r="J20" t="n">
+        <v>100</v>
+      </c>
+      <c r="K20" t="s">
+        <v>45</v>
+      </c>
+      <c r="L20" t="s">
         <v>63</v>
-      </c>
-      <c r="D20" t="n">
-        <v>-21907.805785593</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-21871.9010538407</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10959.9028927965</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.0000218834164508473</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.00348439023508079</v>
-      </c>
-      <c r="I20" t="n">
-        <v>6196.70043012867</v>
-      </c>
-      <c r="J20" t="n">
-        <v>200</v>
-      </c>
-      <c r="K20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L20" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-21922.1562477529</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-21886.2515160007</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10967.0781238764</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0000347159238405809</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.00435265008366597</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5760.70080364324</v>
+      </c>
+      <c r="J21" t="n">
+        <v>100</v>
+      </c>
+      <c r="K21" t="s">
+        <v>45</v>
+      </c>
+      <c r="L21" t="s">
         <v>63</v>
-      </c>
-      <c r="D21" t="n">
-        <v>-21219.4284734558</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-21183.5237417036</v>
-      </c>
-      <c r="F21" t="n">
-        <v>10615.7142367279</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.0000229634382419525</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.00357748912445529</v>
-      </c>
-      <c r="I21" t="n">
-        <v>6053.09816335699</v>
-      </c>
-      <c r="J21" t="n">
-        <v>200</v>
-      </c>
-      <c r="K21" t="s">
-        <v>46</v>
-      </c>
-      <c r="L21" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B22" t="s">
         <v>35</v>
@@ -1932,145 +1928,145 @@
         <v>65</v>
       </c>
       <c r="D22" t="n">
-        <v>-20093.9832449172</v>
+        <v>-18313.964663108</v>
       </c>
       <c r="E22" t="n">
-        <v>-20070.0467570823</v>
+        <v>-18284.0440533145</v>
       </c>
       <c r="F22" t="n">
-        <v>10050.9916224586</v>
+        <v>9161.98233155399</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0000351113442536926</v>
+        <v>0.0000981945220680626</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00439870385864537</v>
+        <v>0.00762717002276283</v>
       </c>
       <c r="I22" t="n">
-        <v>5774.19764879581</v>
+        <v>4615.96261857344</v>
       </c>
       <c r="J22" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C23" t="s">
         <v>65</v>
       </c>
       <c r="D23" t="n">
-        <v>-21446.4359075332</v>
+        <v>-18252.5240091211</v>
       </c>
       <c r="E23" t="n">
-        <v>-21416.5152977397</v>
+        <v>-18216.6192773689</v>
       </c>
       <c r="F23" t="n">
-        <v>10728.2179537666</v>
+        <v>9132.26200456054</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0000351150224151743</v>
+        <v>0.0000987979132283671</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00439406088023143</v>
+        <v>0.00766446564386533</v>
       </c>
       <c r="I23" t="n">
-        <v>5780.09321421133</v>
+        <v>4978.35225415386</v>
       </c>
       <c r="J23" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C24" t="s">
         <v>65</v>
       </c>
       <c r="D24" t="n">
-        <v>-21775.2300244312</v>
+        <v>-18465.0005679739</v>
       </c>
       <c r="E24" t="n">
-        <v>-21739.325292679</v>
+        <v>-18429.0958362217</v>
       </c>
       <c r="F24" t="n">
-        <v>10893.6150122156</v>
+        <v>9238.50028398695</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0000345009050030342</v>
+        <v>0.0000980203316896636</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00431691918580554</v>
+        <v>0.00761623393238203</v>
       </c>
       <c r="I24" t="n">
-        <v>5882.13461935128</v>
+        <v>3949.99748133499</v>
       </c>
       <c r="J24" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
         <v>65</v>
       </c>
       <c r="D25" t="n">
-        <v>-22143.852773775</v>
+        <v>-17933.4795528587</v>
       </c>
       <c r="E25" t="n">
-        <v>-22107.9480420228</v>
+        <v>-17897.5748211065</v>
       </c>
       <c r="F25" t="n">
-        <v>11077.9263868875</v>
+        <v>8972.73977642934</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0000346127833191152</v>
+        <v>0.000098198924570217</v>
       </c>
       <c r="H25" t="n">
-        <v>0.00433154931649469</v>
+        <v>0.00763467765024744</v>
       </c>
       <c r="I25" t="n">
-        <v>5886.36568963006</v>
+        <v>4441.99465545801</v>
       </c>
       <c r="J25" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26">
@@ -2078,460 +2074,460 @@
         <v>38</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D26" t="n">
-        <v>-21922.1562477529</v>
+        <v>-13207.8962469027</v>
       </c>
       <c r="E26" t="n">
-        <v>-21886.2515160007</v>
+        <v>-13177.9756371092</v>
       </c>
       <c r="F26" t="n">
-        <v>10967.0781238764</v>
+        <v>6608.94812345134</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0000344783826509954</v>
+        <v>0.00111705763383032</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00432326276233044</v>
+        <v>0.0243245489718964</v>
       </c>
       <c r="I26" t="n">
-        <v>5890.9308124457</v>
+        <v>1080.31206670788</v>
       </c>
       <c r="J26" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L26" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" t="s">
         <v>35</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D27" t="n">
-        <v>-16711.3634303374</v>
+        <v>-16688.7587376761</v>
       </c>
       <c r="E27" t="n">
-        <v>-16687.4269425026</v>
+        <v>-16658.8381278826</v>
       </c>
       <c r="F27" t="n">
-        <v>8359.6817151687</v>
+        <v>8349.37936883806</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0000998929098308323</v>
+        <v>0.000356775395982169</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00772805708310525</v>
+        <v>0.0133266342961559</v>
       </c>
       <c r="I27" t="n">
-        <v>4908.13119999712</v>
+        <v>2682.36376145129</v>
       </c>
       <c r="J27" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K27" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L27" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C28" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D28" t="n">
-        <v>-17841.2674418593</v>
+        <v>-14446.3970235722</v>
       </c>
       <c r="E28" t="n">
-        <v>-17811.3468320658</v>
+        <v>-14416.4764137787</v>
       </c>
       <c r="F28" t="n">
-        <v>8925.63372092964</v>
+        <v>7228.19851178609</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0000993469544349091</v>
+        <v>0.000499902852630959</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00768000596141435</v>
+        <v>0.0158976783975438</v>
       </c>
       <c r="I28" t="n">
-        <v>4924.38827164208</v>
+        <v>2896.08540539511</v>
       </c>
       <c r="J28" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K28" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L28" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D29" t="n">
-        <v>-18252.5240091211</v>
+        <v>-21640.2971385716</v>
       </c>
       <c r="E29" t="n">
-        <v>-18216.6192773689</v>
+        <v>-21604.3924068193</v>
       </c>
       <c r="F29" t="n">
-        <v>9132.26200456054</v>
+        <v>10826.1485692858</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0000992718992079738</v>
+        <v>0.0000223289814951029</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00767208889444575</v>
+        <v>0.00352418318213981</v>
       </c>
       <c r="I29" t="n">
-        <v>5040.13702461136</v>
+        <v>6207.79574474491</v>
       </c>
       <c r="J29" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C30" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D30" t="n">
-        <v>-18465.0005679739</v>
+        <v>-21775.2300244312</v>
       </c>
       <c r="E30" t="n">
-        <v>-18429.0958362217</v>
+        <v>-21739.325292679</v>
       </c>
       <c r="F30" t="n">
-        <v>9238.50028398695</v>
+        <v>10893.6150122156</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0000989635039139146</v>
+        <v>0.0000345216797439829</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00767762314485683</v>
+        <v>0.00432648233410925</v>
       </c>
       <c r="I30" t="n">
-        <v>5009.62614301722</v>
+        <v>5731.05302519214</v>
       </c>
       <c r="J30" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K30" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D31" t="n">
-        <v>-17933.4795528587</v>
+        <v>-18252.5240091211</v>
       </c>
       <c r="E31" t="n">
-        <v>-17897.5748211065</v>
+        <v>-18216.6192773689</v>
       </c>
       <c r="F31" t="n">
-        <v>8972.73977642934</v>
+        <v>9132.26200456054</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0000984920878496141</v>
+        <v>0.0000995011036329369</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0076470766819771</v>
+        <v>0.00765545525374901</v>
       </c>
       <c r="I31" t="n">
-        <v>4943.99795678676</v>
+        <v>5022.94088249634</v>
       </c>
       <c r="J31" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K31" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B32" t="s">
         <v>35</v>
       </c>
       <c r="C32" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D32" t="n">
-        <v>-19372.7663740109</v>
+        <v>-12886.6841895632</v>
       </c>
       <c r="E32" t="n">
-        <v>-19348.829886176</v>
+        <v>-12850.779457811</v>
       </c>
       <c r="F32" t="n">
-        <v>9690.38318700543</v>
+        <v>6449.34209478161</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0000221746894915632</v>
+        <v>0.00111963335779213</v>
       </c>
       <c r="H32" t="n">
-        <v>0.00350321108239467</v>
+        <v>0.0243288468443096</v>
       </c>
       <c r="I32" t="n">
-        <v>6014.83158238363</v>
+        <v>2760.93161855231</v>
       </c>
       <c r="J32" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L32" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
         <v>35</v>
       </c>
       <c r="C33" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D33" t="n">
-        <v>-20093.9832449172</v>
+        <v>-16459.2335450459</v>
       </c>
       <c r="E33" t="n">
-        <v>-20070.0467570823</v>
+        <v>-16423.3288132937</v>
       </c>
       <c r="F33" t="n">
-        <v>10050.9916224586</v>
+        <v>8235.61677252294</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0000342260571424258</v>
+        <v>0.000359394472998764</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00430731155749105</v>
+        <v>0.0133724090283575</v>
       </c>
       <c r="I33" t="n">
-        <v>5476.6380116998</v>
+        <v>3618.10708966793</v>
       </c>
       <c r="J33" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L33" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B34" t="s">
         <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D34" t="n">
-        <v>-16711.3634303374</v>
+        <v>-14264.3558075108</v>
       </c>
       <c r="E34" t="n">
-        <v>-16687.4269425026</v>
+        <v>-14228.4510757586</v>
       </c>
       <c r="F34" t="n">
-        <v>8359.6817151687</v>
+        <v>7138.17790375541</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0000982743675609389</v>
+        <v>0.000500508197687513</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00768679788169922</v>
+        <v>0.0159272867044439</v>
       </c>
       <c r="I34" t="n">
-        <v>4469.35178960953</v>
+        <v>3664.40653031761</v>
       </c>
       <c r="J34" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L34" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B35" t="s">
         <v>35</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D35" t="n">
-        <v>-10849.6298936207</v>
+        <v>-21922.1562477529</v>
       </c>
       <c r="E35" t="n">
-        <v>-10825.6934057859</v>
+        <v>-21886.2515160007</v>
       </c>
       <c r="F35" t="n">
-        <v>5428.81494681033</v>
+        <v>10967.0781238764</v>
       </c>
       <c r="G35" t="n">
-        <v>0.00112840091247088</v>
+        <v>0.0000345229213145018</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0243402449940381</v>
+        <v>0.00431824406503451</v>
       </c>
       <c r="I35" t="n">
-        <v>2205.49063288371</v>
+        <v>5740.87069061055</v>
       </c>
       <c r="J35" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L35" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B36" t="s">
         <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D36" t="n">
-        <v>-13915.8189354138</v>
+        <v>-13272.5886735945</v>
       </c>
       <c r="E36" t="n">
-        <v>-13891.882447579</v>
+        <v>-13236.6839418423</v>
       </c>
       <c r="F36" t="n">
-        <v>6961.90946770692</v>
+        <v>6642.29433679725</v>
       </c>
       <c r="G36" t="n">
-        <v>0.000381090090987412</v>
+        <v>0.00111681576711409</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0138581890523909</v>
+        <v>0.0243538544181902</v>
       </c>
       <c r="I36" t="n">
-        <v>3183.70218896155</v>
+        <v>-357.943460188679</v>
       </c>
       <c r="J36" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B37" t="s">
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D37" t="n">
-        <v>-11081.523323752</v>
+        <v>-16714.5673553433</v>
       </c>
       <c r="E37" t="n">
-        <v>-11057.5868359172</v>
+        <v>-16678.6626235911</v>
       </c>
       <c r="F37" t="n">
-        <v>5544.76166187601</v>
+        <v>8363.28367767167</v>
       </c>
       <c r="G37" t="n">
-        <v>0.000564191677644273</v>
+        <v>0.000357431509918567</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0172883551699212</v>
+        <v>0.0133298706039886</v>
       </c>
       <c r="I37" t="n">
-        <v>3204.5048231739</v>
+        <v>3142.29683711448</v>
       </c>
       <c r="J37" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B38" t="s">
         <v>35</v>
@@ -2540,74 +2536,74 @@
         <v>62</v>
       </c>
       <c r="D38" t="n">
-        <v>-13348.1714003446</v>
+        <v>-21907.805785593</v>
       </c>
       <c r="E38" t="n">
-        <v>-13318.2507905511</v>
+        <v>-21871.9010538407</v>
       </c>
       <c r="F38" t="n">
-        <v>6679.08570017231</v>
+        <v>10959.9028927965</v>
       </c>
       <c r="G38" t="n">
-        <v>0.000500426622455502</v>
+        <v>0.0000222139181760204</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0158945008810578</v>
+        <v>0.00351165530590862</v>
       </c>
       <c r="I38" t="n">
-        <v>3739.77278199111</v>
+        <v>6160.10829620345</v>
       </c>
       <c r="J38" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L38" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B39" t="s">
         <v>35</v>
       </c>
       <c r="C39" t="s">
+        <v>64</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-22143.852773775</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-22107.9480420228</v>
+      </c>
+      <c r="F39" t="n">
+        <v>11077.9263868875</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.0000344014647730964</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.00432531528279227</v>
+      </c>
+      <c r="I39" t="n">
+        <v>5433.09434519175</v>
+      </c>
+      <c r="J39" t="n">
+        <v>100</v>
+      </c>
+      <c r="K39" t="s">
+        <v>44</v>
+      </c>
+      <c r="L39" t="s">
         <v>63</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-21449.8072377658</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-21419.8866279722</v>
-      </c>
-      <c r="F39" t="n">
-        <v>10729.9036188829</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.0000221376007540136</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.00349886759169113</v>
-      </c>
-      <c r="I39" t="n">
-        <v>6159.92584093635</v>
-      </c>
-      <c r="J39" t="n">
-        <v>200</v>
-      </c>
-      <c r="K39" t="s">
-        <v>45</v>
-      </c>
-      <c r="L39" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B40" t="s">
         <v>35</v>
@@ -2616,112 +2612,112 @@
         <v>65</v>
       </c>
       <c r="D40" t="n">
-        <v>-20490.9474569145</v>
+        <v>-18465.0005679739</v>
       </c>
       <c r="E40" t="n">
-        <v>-20461.026847121</v>
+        <v>-18429.0958362217</v>
       </c>
       <c r="F40" t="n">
-        <v>10250.4737284573</v>
+        <v>9238.50028398695</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0000343006214269721</v>
+        <v>0.0000986189190999559</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00431339941862002</v>
+        <v>0.00763692582301285</v>
       </c>
       <c r="I40" t="n">
-        <v>5687.06929887019</v>
+        <v>4805.78512984572</v>
       </c>
       <c r="J40" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B41" t="s">
         <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D41" t="n">
-        <v>-18400.8070339588</v>
+        <v>-13301.5420123857</v>
       </c>
       <c r="E41" t="n">
-        <v>-18370.8864241653</v>
+        <v>-13265.6372806335</v>
       </c>
       <c r="F41" t="n">
-        <v>9205.40351697942</v>
+        <v>6656.77100619286</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0000987341385758633</v>
+        <v>0.0011173770950026</v>
       </c>
       <c r="H41" t="n">
-        <v>0.00768155294121907</v>
+        <v>0.0242909732837304</v>
       </c>
       <c r="I41" t="n">
-        <v>4999.34986165365</v>
+        <v>589.997045592963</v>
       </c>
       <c r="J41" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L41" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B42" t="s">
         <v>35</v>
       </c>
       <c r="C42" t="s">
+        <v>60</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-16755.7121347858</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-16719.8074030336</v>
+      </c>
+      <c r="F42" t="n">
+        <v>8383.85606739289</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.000357513516856228</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.0133285270844448</v>
+      </c>
+      <c r="I42" t="n">
+        <v>3166.08083140584</v>
+      </c>
+      <c r="J42" t="n">
+        <v>100</v>
+      </c>
+      <c r="K42" t="s">
+        <v>44</v>
+      </c>
+      <c r="L42" t="s">
         <v>59</v>
-      </c>
-      <c r="D42" t="n">
-        <v>-12539.2488040093</v>
-      </c>
-      <c r="E42" t="n">
-        <v>-12509.3281942158</v>
-      </c>
-      <c r="F42" t="n">
-        <v>6274.62440200463</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0.00114716275172289</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.0246198141599958</v>
-      </c>
-      <c r="I42" t="n">
-        <v>2668.16263062273</v>
-      </c>
-      <c r="J42" t="n">
-        <v>200</v>
-      </c>
-      <c r="K42" t="s">
-        <v>45</v>
-      </c>
-      <c r="L42" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B43" t="s">
         <v>35</v>
@@ -2730,297 +2726,31 @@
         <v>61</v>
       </c>
       <c r="D43" t="n">
-        <v>-16142.3583943172</v>
+        <v>-14556.4722711371</v>
       </c>
       <c r="E43" t="n">
-        <v>-16112.4377845237</v>
+        <v>-14520.5675393849</v>
       </c>
       <c r="F43" t="n">
-        <v>8076.17919715859</v>
+        <v>7284.23613556855</v>
       </c>
       <c r="G43" t="n">
-        <v>0.000360553162906069</v>
+        <v>0.000498751522553309</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0133867662019792</v>
+        <v>0.0158513198728056</v>
       </c>
       <c r="I43" t="n">
-        <v>4068.71442510312</v>
+        <v>2727.78027539314</v>
       </c>
       <c r="J43" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L43" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" t="s">
-        <v>35</v>
-      </c>
-      <c r="C44" t="s">
-        <v>62</v>
-      </c>
-      <c r="D44" t="n">
-        <v>-13257.6243799139</v>
-      </c>
-      <c r="E44" t="n">
-        <v>-13227.7037701204</v>
-      </c>
-      <c r="F44" t="n">
-        <v>6633.81218995694</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0.000507826744063959</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.0160418063291914</v>
-      </c>
-      <c r="I44" t="n">
-        <v>3605.56296403186</v>
-      </c>
-      <c r="J44" t="n">
-        <v>200</v>
-      </c>
-      <c r="K44" t="s">
-        <v>45</v>
-      </c>
-      <c r="L44" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>34</v>
-      </c>
-      <c r="B45" t="s">
-        <v>35</v>
-      </c>
-      <c r="C45" t="s">
-        <v>63</v>
-      </c>
-      <c r="D45" t="n">
-        <v>-21603.960640254</v>
-      </c>
-      <c r="E45" t="n">
-        <v>-21574.0400304605</v>
-      </c>
-      <c r="F45" t="n">
-        <v>10806.980320127</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0.0000239608723647867</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.00373800491196438</v>
-      </c>
-      <c r="I45" t="n">
-        <v>4687.19660993523</v>
-      </c>
-      <c r="J45" t="n">
-        <v>200</v>
-      </c>
-      <c r="K45" t="s">
-        <v>45</v>
-      </c>
-      <c r="L45" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>34</v>
-      </c>
-      <c r="B46" t="s">
-        <v>35</v>
-      </c>
-      <c r="C46" t="s">
-        <v>65</v>
-      </c>
-      <c r="D46" t="n">
-        <v>-21950.5756080947</v>
-      </c>
-      <c r="E46" t="n">
-        <v>-21920.6549983012</v>
-      </c>
-      <c r="F46" t="n">
-        <v>10980.2878040474</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0.0000348715203082612</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.00434793195857652</v>
-      </c>
-      <c r="I46" t="n">
-        <v>5680.1669551618</v>
-      </c>
-      <c r="J46" t="n">
-        <v>200</v>
-      </c>
-      <c r="K46" t="s">
-        <v>45</v>
-      </c>
-      <c r="L46" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>34</v>
-      </c>
-      <c r="B47" t="s">
-        <v>35</v>
-      </c>
-      <c r="C47" t="s">
-        <v>66</v>
-      </c>
-      <c r="D47" t="n">
-        <v>-18443.7255754793</v>
-      </c>
-      <c r="E47" t="n">
-        <v>-18413.8049656858</v>
-      </c>
-      <c r="F47" t="n">
-        <v>9226.86278773967</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0.0000985096363115153</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.00765192479069071</v>
-      </c>
-      <c r="I47" t="n">
-        <v>4993.47994505337</v>
-      </c>
-      <c r="J47" t="n">
-        <v>200</v>
-      </c>
-      <c r="K47" t="s">
-        <v>45</v>
-      </c>
-      <c r="L47" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>34</v>
-      </c>
-      <c r="B48" t="s">
-        <v>35</v>
-      </c>
-      <c r="C48" t="s">
         <v>59</v>
-      </c>
-      <c r="D48" t="n">
-        <v>-12745.1907692674</v>
-      </c>
-      <c r="E48" t="n">
-        <v>-12715.2701594739</v>
-      </c>
-      <c r="F48" t="n">
-        <v>6377.59538463372</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.00111955844457315</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.0243926830197835</v>
-      </c>
-      <c r="I48" t="n">
-        <v>3114.93991550959</v>
-      </c>
-      <c r="J48" t="n">
-        <v>200</v>
-      </c>
-      <c r="K48" t="s">
-        <v>45</v>
-      </c>
-      <c r="L48" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>34</v>
-      </c>
-      <c r="B49" t="s">
-        <v>35</v>
-      </c>
-      <c r="C49" t="s">
-        <v>61</v>
-      </c>
-      <c r="D49" t="n">
-        <v>-16194.7563532163</v>
-      </c>
-      <c r="E49" t="n">
-        <v>-16164.8357434228</v>
-      </c>
-      <c r="F49" t="n">
-        <v>8102.37817660814</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0.00035948830300169</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.013377217032468</v>
-      </c>
-      <c r="I49" t="n">
-        <v>4053.15633503966</v>
-      </c>
-      <c r="J49" t="n">
-        <v>200</v>
-      </c>
-      <c r="K49" t="s">
-        <v>45</v>
-      </c>
-      <c r="L49" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>34</v>
-      </c>
-      <c r="B50" t="s">
-        <v>35</v>
-      </c>
-      <c r="C50" t="s">
-        <v>62</v>
-      </c>
-      <c r="D50" t="n">
-        <v>-13577.9900770532</v>
-      </c>
-      <c r="E50" t="n">
-        <v>-13548.0694672597</v>
-      </c>
-      <c r="F50" t="n">
-        <v>6793.9950385266</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0.000495384439992828</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.015801032911702</v>
-      </c>
-      <c r="I50" t="n">
-        <v>3586.41769262345</v>
-      </c>
-      <c r="J50" t="n">
-        <v>200</v>
-      </c>
-      <c r="K50" t="s">
-        <v>45</v>
-      </c>
-      <c r="L50" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3042,42 +2772,65 @@
         <v>19</v>
       </c>
       <c r="C1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" t="s">
         <v>67</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>68</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>69</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>70</v>
-      </c>
-      <c r="G1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
         <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E2" t="n">
-        <v>0.21875</v>
+        <v>1</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>73</v>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -3093,147 +2846,147 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s">
         <v>20</v>
       </c>
       <c r="D1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" t="s">
         <v>43</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>74</v>
       </c>
-      <c r="F1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" t="s">
         <v>75</v>
-      </c>
-      <c r="H1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000656408314981865</v>
+        <v>0.000672832847487877</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00050412668325973</v>
+        <v>0.000499902852630959</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0179000609752528</v>
+        <v>0.0180301772278061</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0159681536051246</v>
+        <v>0.0158976783975438</v>
       </c>
       <c r="H2" t="n">
-        <v>-13365.2312330908</v>
+        <v>-14777.6552725016</v>
       </c>
       <c r="I2" t="n">
-        <v>-13302.8978901293</v>
+        <v>-14446.3970235722</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000668545455393949</v>
+        <v>0.000657732261677535</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000510320566076767</v>
+        <v>0.000498742008315416</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0180875387600556</v>
+        <v>0.0178438424627864</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0161365366418438</v>
+        <v>0.0158788667921911</v>
       </c>
       <c r="H3" t="n">
-        <v>-14052.0782054458</v>
+        <v>-14713.8267772652</v>
       </c>
       <c r="I3" t="n">
-        <v>-13915.8189354138</v>
+        <v>-14355.3764155415</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0000519099448818156</v>
+        <v>0.0000494441411765139</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0000343006214269721</v>
+        <v>0.0000345216797439829</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00519211134826075</v>
+        <v>0.00504260874953519</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00431339941862002</v>
+        <v>0.00432531528279227</v>
       </c>
       <c r="H4" t="n">
-        <v>-19835.3262890814</v>
+        <v>-20872.4095067455</v>
       </c>
       <c r="I4" t="n">
-        <v>-20093.9832449172</v>
+        <v>-21775.2300244312</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0000522426996523246</v>
+        <v>0.0000516863758482536</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0000346127833191152</v>
+        <v>0.0000344384977339093</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00519982123193084</v>
+        <v>0.00516262538479136</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00433154931649469</v>
+        <v>0.0043307669738517</v>
       </c>
       <c r="H5" t="n">
-        <v>-20120.7875857852</v>
+        <v>-20611.2017348122</v>
       </c>
       <c r="I5" t="n">
-        <v>-21086.222814587</v>
+        <v>-21684.449904215</v>
       </c>
     </row>
   </sheetData>
@@ -3249,58 +3002,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" t="s">
         <v>77</v>
       </c>
-      <c r="C1" t="s">
-        <v>78</v>
-      </c>
       <c r="D1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
         <v>45</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>66.6666666666667</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
         <v>45</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>100</v>
+        <v>66.6666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/results/tscv/consolidated/NF_vs_Standard_GARCH_Comparison.xlsx
+++ b/results/tscv/consolidated/NF_vs_Standard_GARCH_Comparison.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t xml:space="preserve">Question</t>
   </si>
@@ -36,37 +36,37 @@
     <t xml:space="preserve">Overall mean MSE - Standard</t>
   </si>
   <si>
-    <t xml:space="preserve">0.000354709318762894</t>
+    <t xml:space="preserve">0.000260016428504941</t>
   </si>
   <si>
     <t xml:space="preserve">Overall mean MSE - NF-GARCH</t>
   </si>
   <si>
-    <t xml:space="preserve">0.000430403906144569</t>
+    <t xml:space="preserve">0.000304009368893895</t>
   </si>
   <si>
     <t xml:space="preserve">Overall mean AIC - Standard</t>
   </si>
   <si>
-    <t xml:space="preserve">-17662.5142560387</t>
+    <t xml:space="preserve">-18206.6196931364</t>
   </si>
   <si>
     <t xml:space="preserve">Overall mean AIC - NF-GARCH</t>
   </si>
   <si>
-    <t xml:space="preserve">-17147.8374747076</t>
+    <t xml:space="preserve">-17945.9623486173</t>
   </si>
   <si>
     <t xml:space="preserve">NF-GARCH wins (lower MSE)</t>
   </si>
   <si>
-    <t xml:space="preserve">6</t>
+    <t xml:space="preserve">13</t>
   </si>
   <si>
     <t xml:space="preserve">Standard GARCH wins (lower MSE)</t>
   </si>
   <si>
-    <t xml:space="preserve">12</t>
+    <t xml:space="preserve">21</t>
   </si>
   <si>
     <t xml:space="preserve">Overall winner</t>
@@ -195,15 +195,27 @@
     <t xml:space="preserve">Asset_Class</t>
   </si>
   <si>
+    <t xml:space="preserve">X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity</t>
+  </si>
+  <si>
     <t xml:space="preserve">NVDA</t>
   </si>
   <si>
-    <t xml:space="preserve">Equity</t>
-  </si>
-  <si>
     <t xml:space="preserve">MSFT</t>
   </si>
   <si>
+    <t xml:space="preserve">PG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WMT</t>
+  </si>
+  <si>
     <t xml:space="preserve">AMZN</t>
   </si>
   <si>
@@ -216,7 +228,16 @@
     <t xml:space="preserve">GBPUSD</t>
   </si>
   <si>
+    <t xml:space="preserve">GBPCNY</t>
+  </si>
+  <si>
     <t xml:space="preserve">USDZAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GBPZAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EURZAR</t>
   </si>
   <si>
     <t xml:space="preserve">Test_Type</t>
@@ -722,46 +743,46 @@
         <v>35</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>-17855.0642576084</v>
+        <v>-18349.3078348571</v>
       </c>
       <c r="E2" t="n">
-        <v>-17855.0642576084</v>
+        <v>-18349.3078348571</v>
       </c>
       <c r="F2" t="n">
-        <v>-17819.1595258562</v>
+        <v>-18313.4031031049</v>
       </c>
       <c r="G2" t="n">
-        <v>-17819.1595258562</v>
+        <v>-18313.4031031049</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000354812739410202</v>
+        <v>0.000259747235715852</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000354083088947051</v>
+        <v>0.000259663674809237</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0114907861087824</v>
+        <v>0.00994191505748576</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0114868949753609</v>
+        <v>0.00993274054082717</v>
       </c>
       <c r="L2" t="n">
-        <v>8933.53212880421</v>
+        <v>9180.65391742856</v>
       </c>
       <c r="M2" t="n">
-        <v>8933.53212880421</v>
+        <v>9180.65391742856</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00000000000363797880709171</v>
+        <v>-0.00000000000727595761418343</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.206067582984568</v>
+        <v>-0.0321804375126556</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0338745451215462</v>
+        <v>-0.0923664181187208</v>
       </c>
     </row>
     <row r="3">
@@ -772,46 +793,46 @@
         <v>35</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>-17546.387452374</v>
+        <v>-18109.1741651016</v>
       </c>
       <c r="E3" t="n">
-        <v>-17546.387452374</v>
+        <v>-18109.1741651016</v>
       </c>
       <c r="F3" t="n">
-        <v>-17510.4827206218</v>
+        <v>-18073.2694333493</v>
       </c>
       <c r="G3" t="n">
-        <v>-17510.4827206217</v>
+        <v>-18073.2694333493</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000355981298891738</v>
+        <v>0.000260915066165745</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000355303039142247</v>
+        <v>0.000260404852138214</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0115224438911848</v>
+        <v>0.00997997001646905</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0115272723594018</v>
+        <v>0.0099567916684556</v>
       </c>
       <c r="L3" t="n">
-        <v>8779.19372618698</v>
+        <v>9060.58708255077</v>
       </c>
       <c r="M3" t="n">
-        <v>8779.19372618698</v>
+        <v>9060.58708255078</v>
       </c>
       <c r="N3" t="n">
         <v>0.00000000000727595761418343</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.190896129436118</v>
+        <v>-0.195931075531961</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0418873439125912</v>
+        <v>-0.232789323963552</v>
       </c>
     </row>
     <row r="4">
@@ -822,26 +843,26 @@
         <v>35</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>-17303.1040922302</v>
+        <v>-18116.6118143257</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="n">
-        <v>-17267.199360478</v>
+        <v>-18080.7070825735</v>
       </c>
       <c r="G4"/>
       <c r="H4" t="n">
-        <v>0.000502923399449053</v>
+        <v>0.000335028645504487</v>
       </c>
       <c r="I4"/>
       <c r="J4" t="n">
-        <v>0.0140006563624044</v>
+        <v>0.0112857145283358</v>
       </c>
       <c r="K4"/>
       <c r="L4" t="n">
-        <v>8657.55204611511</v>
+        <v>9064.30590716285</v>
       </c>
       <c r="M4"/>
       <c r="N4"/>
@@ -856,27 +877,27 @@
         <v>35</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D5"/>
       <c r="E5" t="n">
-        <v>-17512.3222721118</v>
+        <v>-18122.3502558445</v>
       </c>
       <c r="F5"/>
       <c r="G5" t="n">
-        <v>-17476.4175403596</v>
+        <v>-18086.4455240923</v>
       </c>
       <c r="H5"/>
       <c r="I5" t="n">
-        <v>0.000354766034996837</v>
+        <v>0.000259989291420165</v>
       </c>
       <c r="J5"/>
       <c r="K5" t="n">
-        <v>0.0115046808319871</v>
+        <v>0.00994731293399504</v>
       </c>
       <c r="L5"/>
       <c r="M5" t="n">
-        <v>8762.16113605591</v>
+        <v>9067.17512792227</v>
       </c>
       <c r="N5"/>
       <c r="O5"/>
@@ -890,26 +911,26 @@
         <v>35</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>-14781.0173360503</v>
+        <v>-16347.3155700878</v>
       </c>
       <c r="E6"/>
       <c r="F6" t="n">
-        <v>-14751.0967262568</v>
+        <v>-16317.3949602943</v>
       </c>
       <c r="G6"/>
       <c r="H6" t="n">
-        <v>0.000657911960814483</v>
+        <v>0.000470237827813931</v>
       </c>
       <c r="I6"/>
       <c r="J6" t="n">
-        <v>0.0178496205551987</v>
+        <v>0.0143034536367556</v>
       </c>
       <c r="K6"/>
       <c r="L6" t="n">
-        <v>7395.50866802516</v>
+        <v>8178.65778504392</v>
       </c>
       <c r="M6"/>
       <c r="N6"/>
@@ -924,27 +945,27 @@
         <v>35</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D7"/>
       <c r="E7" t="n">
-        <v>-17736.2830420607</v>
+        <v>-18245.6465167424</v>
       </c>
       <c r="F7"/>
       <c r="G7" t="n">
-        <v>-17706.3624322672</v>
+        <v>-18215.7259069489</v>
       </c>
       <c r="H7"/>
       <c r="I7" t="n">
-        <v>0.000354685111965443</v>
+        <v>0.000260007895652147</v>
       </c>
       <c r="J7"/>
       <c r="K7" t="n">
-        <v>0.0114940875284057</v>
+        <v>0.00993855448798683</v>
       </c>
       <c r="L7"/>
       <c r="M7" t="n">
-        <v>8873.14152103034</v>
+        <v>9127.82325837121</v>
       </c>
       <c r="N7"/>
       <c r="O7"/>
@@ -983,16 +1004,16 @@
         <v>44</v>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C2" t="n">
-        <v>-17147.8374747076</v>
+        <v>-17945.9623486173</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000430403906144569</v>
+        <v>0.000304009368893895</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0129794561529229</v>
+        <v>0.0108216636324885</v>
       </c>
     </row>
     <row r="3">
@@ -1000,16 +1021,16 @@
         <v>45</v>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>-17662.5142560387</v>
+        <v>-18206.6196931364</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000354709318762894</v>
+        <v>0.000260016428504941</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0115032339237889</v>
+        <v>0.00994384990781616</v>
       </c>
     </row>
   </sheetData>
@@ -1048,13 +1069,13 @@
         <v>35</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>36.3636363636364</v>
       </c>
     </row>
     <row r="3">
@@ -1065,13 +1086,13 @@
         <v>35</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>36.3636363636364</v>
       </c>
     </row>
     <row r="4">
@@ -1082,13 +1103,13 @@
         <v>35</v>
       </c>
       <c r="C4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
       <c r="E4" t="n">
-        <v>33.3333333333333</v>
+        <v>42.8571428571429</v>
       </c>
     </row>
     <row r="5">
@@ -1099,13 +1120,13 @@
         <v>35</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>66.6666666666667</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1472,22 +1493,22 @@
         <v>61</v>
       </c>
       <c r="D10" t="n">
-        <v>-14446.3970235722</v>
+        <v>-19157.8116926813</v>
       </c>
       <c r="E10" t="n">
-        <v>-14416.4764137787</v>
+        <v>-19127.8910828878</v>
       </c>
       <c r="F10" t="n">
-        <v>7228.19851178609</v>
+        <v>9583.90584634064</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000497147014810391</v>
+        <v>0.000173013615525479</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0158477359464996</v>
+        <v>0.00874260227245424</v>
       </c>
       <c r="I10" t="n">
-        <v>2859.0613648566</v>
+        <v>3643.1725312778</v>
       </c>
       <c r="J10" t="n">
         <v>100</v>
@@ -1510,22 +1531,22 @@
         <v>61</v>
       </c>
       <c r="D11" t="n">
-        <v>-14264.3558075108</v>
+        <v>-18960.5341690539</v>
       </c>
       <c r="E11" t="n">
-        <v>-14228.4510757586</v>
+        <v>-18924.6294373017</v>
       </c>
       <c r="F11" t="n">
-        <v>7138.17790375541</v>
+        <v>9486.26708452694</v>
       </c>
       <c r="G11" t="n">
-        <v>0.000500250823983806</v>
+        <v>0.000173087239561415</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0159769806422821</v>
+        <v>0.00872969831381267</v>
       </c>
       <c r="I11" t="n">
-        <v>3622.5691129771</v>
+        <v>4423.75010108033</v>
       </c>
       <c r="J11" t="n">
         <v>100</v>
@@ -1548,22 +1569,22 @@
         <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>-14556.4722711371</v>
+        <v>-19203.1063159103</v>
       </c>
       <c r="E12" t="n">
-        <v>-14520.5675393849</v>
+        <v>-19167.2015841581</v>
       </c>
       <c r="F12" t="n">
-        <v>7284.23613556855</v>
+        <v>9607.55315795517</v>
       </c>
       <c r="G12" t="n">
-        <v>0.000497233192647025</v>
+        <v>0.000172886631064179</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0158559419937669</v>
+        <v>0.0087375433275934</v>
       </c>
       <c r="I12" t="n">
-        <v>2346.57626978034</v>
+        <v>2602.69319067766</v>
       </c>
       <c r="J12" t="n">
         <v>100</v>
@@ -1586,22 +1607,22 @@
         <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>-14011.7133296657</v>
+        <v>-19180.8529014042</v>
       </c>
       <c r="E13" t="n">
-        <v>-13975.8085979135</v>
+        <v>-19144.948169652</v>
       </c>
       <c r="F13" t="n">
-        <v>7011.85666483284</v>
+        <v>9596.42645070209</v>
       </c>
       <c r="G13" t="n">
-        <v>0.000501215976354351</v>
+        <v>0.00017313235798049</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0159017915906153</v>
+        <v>0.00875685996235977</v>
       </c>
       <c r="I13" t="n">
-        <v>3386.24190851075</v>
+        <v>3923.38261139027</v>
       </c>
       <c r="J13" t="n">
         <v>100</v>
@@ -1624,22 +1645,22 @@
         <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>-21728.6026698585</v>
+        <v>-15460.5927395456</v>
       </c>
       <c r="E14" t="n">
-        <v>-21698.682060065</v>
+        <v>-15430.6721297521</v>
       </c>
       <c r="F14" t="n">
-        <v>10869.3013349292</v>
+        <v>7735.2963697728</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0000223627813478594</v>
+        <v>0.000427681479269848</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00353359621682163</v>
+        <v>0.0149152884921024</v>
       </c>
       <c r="I14" t="n">
-        <v>6037.12475217081</v>
+        <v>2363.64215529572</v>
       </c>
       <c r="J14" t="n">
         <v>100</v>
@@ -1648,7 +1669,7 @@
         <v>45</v>
       </c>
       <c r="L14" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -1662,22 +1683,22 @@
         <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>-21640.2971385716</v>
+        <v>-15123.4937397722</v>
       </c>
       <c r="E15" t="n">
-        <v>-21604.3924068193</v>
+        <v>-15087.58900802</v>
       </c>
       <c r="F15" t="n">
-        <v>10826.1485692858</v>
+        <v>7567.7468698861</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0000223129991188355</v>
+        <v>0.000428406791426137</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00352247019300576</v>
+        <v>0.0149544818335781</v>
       </c>
       <c r="I15" t="n">
-        <v>6204.93485317718</v>
+        <v>3610.24278613498</v>
       </c>
       <c r="J15" t="n">
         <v>100</v>
@@ -1686,7 +1707,7 @@
         <v>45</v>
       </c>
       <c r="L15" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16">
@@ -1700,22 +1721,22 @@
         <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>-21907.805785593</v>
+        <v>-15580.3567037644</v>
       </c>
       <c r="E16" t="n">
-        <v>-21871.9010538407</v>
+        <v>-15544.4519720122</v>
       </c>
       <c r="F16" t="n">
-        <v>10959.9028927965</v>
+        <v>7796.17835188222</v>
       </c>
       <c r="G16" t="n">
-        <v>0.000022227606782021</v>
+        <v>0.00042676706002737</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00351111212333665</v>
+        <v>0.0148934691122633</v>
       </c>
       <c r="I16" t="n">
-        <v>5760.26085402423</v>
+        <v>2056.10345688917</v>
       </c>
       <c r="J16" t="n">
         <v>100</v>
@@ -1724,7 +1745,7 @@
         <v>45</v>
       </c>
       <c r="L16" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
@@ -1738,22 +1759,22 @@
         <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>-21219.4284734558</v>
+        <v>-15518.5292120059</v>
       </c>
       <c r="E17" t="n">
-        <v>-21183.5237417036</v>
+        <v>-15482.6244802537</v>
       </c>
       <c r="F17" t="n">
-        <v>10615.7142367279</v>
+        <v>7765.26460600297</v>
       </c>
       <c r="G17" t="n">
-        <v>0.000022136450465134</v>
+        <v>0.000428603062058782</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00350657493240071</v>
+        <v>0.0149310540224382</v>
       </c>
       <c r="I17" t="n">
-        <v>6022.36885159423</v>
+        <v>2899.94872914287</v>
       </c>
       <c r="J17" t="n">
         <v>100</v>
@@ -1762,7 +1783,7 @@
         <v>45</v>
       </c>
       <c r="L17" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18">
@@ -1773,25 +1794,25 @@
         <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D18" t="n">
-        <v>-22032.0789112467</v>
+        <v>-18235.7141496069</v>
       </c>
       <c r="E18" t="n">
-        <v>-22002.1583014532</v>
+        <v>-18205.7935398134</v>
       </c>
       <c r="F18" t="n">
-        <v>11021.0394556234</v>
+        <v>9122.85707480347</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0000343920616004835</v>
+        <v>0.000203458276818574</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00432101987130455</v>
+        <v>0.00921809850704005</v>
       </c>
       <c r="I18" t="n">
-        <v>5056.18016341248</v>
+        <v>4253.97546772883</v>
       </c>
       <c r="J18" t="n">
         <v>100</v>
@@ -1800,7 +1821,7 @@
         <v>45</v>
       </c>
       <c r="L18" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -1811,25 +1832,25 @@
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D19" t="n">
-        <v>-21775.2300244312</v>
+        <v>-18150.2559713468</v>
       </c>
       <c r="E19" t="n">
-        <v>-21739.325292679</v>
+        <v>-18114.3512395946</v>
       </c>
       <c r="F19" t="n">
-        <v>10893.6150122156</v>
+        <v>9081.12798567339</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0000344259538106167</v>
+        <v>0.000202986720510785</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00433438276462643</v>
+        <v>0.00919888154432621</v>
       </c>
       <c r="I19" t="n">
-        <v>5715.1088056586</v>
+        <v>4514.38424885621</v>
       </c>
       <c r="J19" t="n">
         <v>100</v>
@@ -1838,7 +1859,7 @@
         <v>45</v>
       </c>
       <c r="L19" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20">
@@ -1849,25 +1870,25 @@
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D20" t="n">
-        <v>-22143.852773775</v>
+        <v>-18318.3939502536</v>
       </c>
       <c r="E20" t="n">
-        <v>-22107.9480420228</v>
+        <v>-18282.4892185014</v>
       </c>
       <c r="F20" t="n">
-        <v>11077.9263868875</v>
+        <v>9165.19697512682</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0000344510416572018</v>
+        <v>0.000204102369492446</v>
       </c>
       <c r="H20" t="n">
-        <v>0.00432715118307698</v>
+        <v>0.00920727659937519</v>
       </c>
       <c r="I20" t="n">
-        <v>5065.35447795538</v>
+        <v>3444.54049179887</v>
       </c>
       <c r="J20" t="n">
         <v>100</v>
@@ -1876,7 +1897,7 @@
         <v>45</v>
       </c>
       <c r="L20" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21">
@@ -1887,25 +1908,25 @@
         <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D21" t="n">
-        <v>-21922.1562477529</v>
+        <v>-18195.3717021399</v>
       </c>
       <c r="E21" t="n">
-        <v>-21886.2515160007</v>
+        <v>-18159.4669703877</v>
       </c>
       <c r="F21" t="n">
-        <v>10967.0781238764</v>
+        <v>9103.68585106996</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0000347159238405809</v>
+        <v>0.00020342880653416</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00435265008366597</v>
+        <v>0.00921146770665919</v>
       </c>
       <c r="I21" t="n">
-        <v>5760.70080364324</v>
+        <v>4330.06476507982</v>
       </c>
       <c r="J21" t="n">
         <v>100</v>
@@ -1914,7 +1935,7 @@
         <v>45</v>
       </c>
       <c r="L21" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22">
@@ -1925,25 +1946,25 @@
         <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D22" t="n">
-        <v>-18313.964663108</v>
+        <v>-14446.3970235722</v>
       </c>
       <c r="E22" t="n">
-        <v>-18284.0440533145</v>
+        <v>-14416.4764137787</v>
       </c>
       <c r="F22" t="n">
-        <v>9161.98233155399</v>
+        <v>7228.19851178609</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0000981945220680626</v>
+        <v>0.00049769364287311</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00762717002276283</v>
+        <v>0.0158601719035652</v>
       </c>
       <c r="I22" t="n">
-        <v>4615.96261857344</v>
+        <v>2842.31657238051</v>
       </c>
       <c r="J22" t="n">
         <v>100</v>
@@ -1952,7 +1973,7 @@
         <v>45</v>
       </c>
       <c r="L22" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
@@ -1963,25 +1984,25 @@
         <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D23" t="n">
-        <v>-18252.5240091211</v>
+        <v>-14264.3558075108</v>
       </c>
       <c r="E23" t="n">
-        <v>-18216.6192773689</v>
+        <v>-14228.4510757586</v>
       </c>
       <c r="F23" t="n">
-        <v>9132.26200456054</v>
+        <v>7138.17790375541</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0000987979132283671</v>
+        <v>0.000502040195227635</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00766446564386533</v>
+        <v>0.0159793794008685</v>
       </c>
       <c r="I23" t="n">
-        <v>4978.35225415386</v>
+        <v>3586.83885815395</v>
       </c>
       <c r="J23" t="n">
         <v>100</v>
@@ -1990,7 +2011,7 @@
         <v>45</v>
       </c>
       <c r="L23" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24">
@@ -2001,25 +2022,25 @@
         <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D24" t="n">
-        <v>-18465.0005679739</v>
+        <v>-14556.4722711371</v>
       </c>
       <c r="E24" t="n">
-        <v>-18429.0958362217</v>
+        <v>-14520.5675393849</v>
       </c>
       <c r="F24" t="n">
-        <v>9238.50028398695</v>
+        <v>7284.23613556855</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0000980203316896636</v>
+        <v>0.000498249795331508</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00761623393238203</v>
+        <v>0.0158890025178234</v>
       </c>
       <c r="I24" t="n">
-        <v>3949.99748133499</v>
+        <v>2355.91417472123</v>
       </c>
       <c r="J24" t="n">
         <v>100</v>
@@ -2028,7 +2049,7 @@
         <v>45</v>
       </c>
       <c r="L24" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25">
@@ -2039,25 +2060,25 @@
         <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>-17933.4795528587</v>
+        <v>-14011.7133296657</v>
       </c>
       <c r="E25" t="n">
-        <v>-17897.5748211065</v>
+        <v>-13975.8085979135</v>
       </c>
       <c r="F25" t="n">
-        <v>8972.73977642934</v>
+        <v>7011.85666483284</v>
       </c>
       <c r="G25" t="n">
-        <v>0.000098198924570217</v>
+        <v>0.000499991136959939</v>
       </c>
       <c r="H25" t="n">
-        <v>0.00763467765024744</v>
+        <v>0.0158933858264112</v>
       </c>
       <c r="I25" t="n">
-        <v>4441.99465545801</v>
+        <v>3306.28635968502</v>
       </c>
       <c r="J25" t="n">
         <v>100</v>
@@ -2066,7 +2087,7 @@
         <v>45</v>
       </c>
       <c r="L25" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26">
@@ -2077,31 +2098,31 @@
         <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D26" t="n">
-        <v>-13207.8962469027</v>
+        <v>-21728.6026698585</v>
       </c>
       <c r="E26" t="n">
-        <v>-13177.9756371092</v>
+        <v>-21698.682060065</v>
       </c>
       <c r="F26" t="n">
-        <v>6608.94812345134</v>
+        <v>10869.3013349292</v>
       </c>
       <c r="G26" t="n">
-        <v>0.00111705763383032</v>
+        <v>0.00002224493681791</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0243245489718964</v>
+        <v>0.00352422306481148</v>
       </c>
       <c r="I26" t="n">
-        <v>1080.31206670788</v>
+        <v>6096.5099485607</v>
       </c>
       <c r="J26" t="n">
         <v>100</v>
       </c>
       <c r="K26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L26" t="s">
         <v>59</v>
@@ -2109,37 +2130,37 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B27" t="s">
         <v>35</v>
       </c>
       <c r="C27" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D27" t="n">
-        <v>-16688.7587376761</v>
+        <v>-21640.2971385716</v>
       </c>
       <c r="E27" t="n">
-        <v>-16658.8381278826</v>
+        <v>-21604.3924068193</v>
       </c>
       <c r="F27" t="n">
-        <v>8349.37936883806</v>
+        <v>10826.1485692858</v>
       </c>
       <c r="G27" t="n">
-        <v>0.000356775395982169</v>
+        <v>0.0000223421053000878</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0133266342961559</v>
+        <v>0.00352610608699801</v>
       </c>
       <c r="I27" t="n">
-        <v>2682.36376145129</v>
+        <v>6178.31428020855</v>
       </c>
       <c r="J27" t="n">
         <v>100</v>
       </c>
       <c r="K27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L27" t="s">
         <v>59</v>
@@ -2147,37 +2168,37 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B28" t="s">
         <v>35</v>
       </c>
       <c r="C28" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D28" t="n">
-        <v>-14446.3970235722</v>
+        <v>-21907.805785593</v>
       </c>
       <c r="E28" t="n">
-        <v>-14416.4764137787</v>
+        <v>-21871.9010538407</v>
       </c>
       <c r="F28" t="n">
-        <v>7228.19851178609</v>
+        <v>10959.9028927965</v>
       </c>
       <c r="G28" t="n">
-        <v>0.000499902852630959</v>
+        <v>0.0000221600255827328</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0158976783975438</v>
+        <v>0.00350968280879987</v>
       </c>
       <c r="I28" t="n">
-        <v>2896.08540539511</v>
+        <v>5709.43257932618</v>
       </c>
       <c r="J28" t="n">
         <v>100</v>
       </c>
       <c r="K28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L28" t="s">
         <v>59</v>
@@ -2185,78 +2206,78 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29" t="s">
         <v>35</v>
       </c>
       <c r="C29" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D29" t="n">
-        <v>-21640.2971385716</v>
+        <v>-21219.4284734558</v>
       </c>
       <c r="E29" t="n">
-        <v>-21604.3924068193</v>
+        <v>-21183.5237417036</v>
       </c>
       <c r="F29" t="n">
-        <v>10826.1485692858</v>
+        <v>10615.7142367279</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0000223289814951029</v>
+        <v>0.0000221541057262932</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00352418318213981</v>
+        <v>0.00350848543062029</v>
       </c>
       <c r="I29" t="n">
-        <v>6207.79574474491</v>
+        <v>6021.95391283566</v>
       </c>
       <c r="J29" t="n">
         <v>100</v>
       </c>
       <c r="K29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L29" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B30" t="s">
         <v>35</v>
       </c>
       <c r="C30" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D30" t="n">
-        <v>-21775.2300244312</v>
+        <v>-22032.0789112467</v>
       </c>
       <c r="E30" t="n">
-        <v>-21739.325292679</v>
+        <v>-22002.1583014532</v>
       </c>
       <c r="F30" t="n">
-        <v>10893.6150122156</v>
+        <v>11021.0394556234</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0000345216797439829</v>
+        <v>0.0000344683420529472</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00432648233410925</v>
+        <v>0.00431989173585829</v>
       </c>
       <c r="I30" t="n">
-        <v>5731.05302519214</v>
+        <v>5097.79860793647</v>
       </c>
       <c r="J30" t="n">
         <v>100</v>
       </c>
       <c r="K30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L30" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31">
@@ -2267,224 +2288,224 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D31" t="n">
-        <v>-18252.5240091211</v>
+        <v>-21775.2300244312</v>
       </c>
       <c r="E31" t="n">
-        <v>-18216.6192773689</v>
+        <v>-21739.325292679</v>
       </c>
       <c r="F31" t="n">
-        <v>9132.26200456054</v>
+        <v>10893.6150122156</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0000995011036329369</v>
+        <v>0.0000344984675490826</v>
       </c>
       <c r="H31" t="n">
-        <v>0.00765545525374901</v>
+        <v>0.00432207435450189</v>
       </c>
       <c r="I31" t="n">
-        <v>5022.94088249634</v>
+        <v>5700.80860835781</v>
       </c>
       <c r="J31" t="n">
         <v>100</v>
       </c>
       <c r="K31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L31" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B32" t="s">
         <v>35</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D32" t="n">
-        <v>-12886.6841895632</v>
+        <v>-22143.852773775</v>
       </c>
       <c r="E32" t="n">
-        <v>-12850.779457811</v>
+        <v>-22107.9480420228</v>
       </c>
       <c r="F32" t="n">
-        <v>6449.34209478161</v>
+        <v>11077.9263868875</v>
       </c>
       <c r="G32" t="n">
-        <v>0.00111963335779213</v>
+        <v>0.0000342857531805018</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0243288468443096</v>
+        <v>0.00430769414472758</v>
       </c>
       <c r="I32" t="n">
-        <v>2760.93161855231</v>
+        <v>5041.87983131908</v>
       </c>
       <c r="J32" t="n">
         <v>100</v>
       </c>
       <c r="K32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L32" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B33" t="s">
         <v>35</v>
       </c>
       <c r="C33" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D33" t="n">
-        <v>-16459.2335450459</v>
+        <v>-21922.1562477529</v>
       </c>
       <c r="E33" t="n">
-        <v>-16423.3288132937</v>
+        <v>-21886.2515160007</v>
       </c>
       <c r="F33" t="n">
-        <v>8235.61677252294</v>
+        <v>10967.0781238764</v>
       </c>
       <c r="G33" t="n">
-        <v>0.000359394472998764</v>
+        <v>0.0000345035612522978</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0133724090283575</v>
+        <v>0.00433129937319265</v>
       </c>
       <c r="I33" t="n">
-        <v>3618.10708966793</v>
+        <v>5731.67950700371</v>
       </c>
       <c r="J33" t="n">
         <v>100</v>
       </c>
       <c r="K33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L33" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B34" t="s">
         <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>-14264.3558075108</v>
+        <v>-21823.6918893993</v>
       </c>
       <c r="E34" t="n">
-        <v>-14228.4510757586</v>
+        <v>-21793.7712796058</v>
       </c>
       <c r="F34" t="n">
-        <v>7138.17790375541</v>
+        <v>10916.8459446997</v>
       </c>
       <c r="G34" t="n">
-        <v>0.000500508197687513</v>
+        <v>0.0000306755181037404</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0159272867044439</v>
+        <v>0.00409986758603111</v>
       </c>
       <c r="I34" t="n">
-        <v>3664.40653031761</v>
+        <v>5721.0563399417</v>
       </c>
       <c r="J34" t="n">
         <v>100</v>
       </c>
       <c r="K34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L34" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B35" t="s">
         <v>35</v>
       </c>
       <c r="C35" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D35" t="n">
-        <v>-21922.1562477529</v>
+        <v>-21710.3566868651</v>
       </c>
       <c r="E35" t="n">
-        <v>-21886.2515160007</v>
+        <v>-21674.4519551129</v>
       </c>
       <c r="F35" t="n">
-        <v>10967.0781238764</v>
+        <v>10861.1783434325</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0000345229213145018</v>
+        <v>0.0000306010451063538</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00431824406503451</v>
+        <v>0.00409407936146841</v>
       </c>
       <c r="I35" t="n">
-        <v>5740.87069061055</v>
+        <v>5881.40296120815</v>
       </c>
       <c r="J35" t="n">
         <v>100</v>
       </c>
       <c r="K35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L35" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
         <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>-13272.5886735945</v>
+        <v>-21895.756317562</v>
       </c>
       <c r="E36" t="n">
-        <v>-13236.6839418423</v>
+        <v>-21859.8515858098</v>
       </c>
       <c r="F36" t="n">
-        <v>6642.29433679725</v>
+        <v>10953.878158781</v>
       </c>
       <c r="G36" t="n">
-        <v>0.00111681576711409</v>
+        <v>0.0000305834384341713</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0243538544181902</v>
+        <v>0.00409211429091625</v>
       </c>
       <c r="I36" t="n">
-        <v>-357.943460188679</v>
+        <v>4020.14439578973</v>
       </c>
       <c r="J36" t="n">
         <v>100</v>
       </c>
       <c r="K36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L36" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37">
@@ -2495,110 +2516,110 @@
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D37" t="n">
-        <v>-16714.5673553433</v>
+        <v>-22012.2166080391</v>
       </c>
       <c r="E37" t="n">
-        <v>-16678.6626235911</v>
+        <v>-21976.3118762869</v>
       </c>
       <c r="F37" t="n">
-        <v>8363.28367767167</v>
+        <v>11012.1083040196</v>
       </c>
       <c r="G37" t="n">
-        <v>0.000357431509918567</v>
+        <v>0.0000306012707234437</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0133298706039886</v>
+        <v>0.00409669560160542</v>
       </c>
       <c r="I37" t="n">
-        <v>3142.29683711448</v>
+        <v>5724.04268312446</v>
       </c>
       <c r="J37" t="n">
         <v>100</v>
       </c>
       <c r="K37" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L37" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B38" t="s">
         <v>35</v>
       </c>
       <c r="C38" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D38" t="n">
-        <v>-21907.805785593</v>
+        <v>-18313.964663108</v>
       </c>
       <c r="E38" t="n">
-        <v>-21871.9010538407</v>
+        <v>-18284.0440533145</v>
       </c>
       <c r="F38" t="n">
-        <v>10959.9028927965</v>
+        <v>9161.98233155399</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0000222139181760204</v>
+        <v>0.0000985433666406015</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00351165530590862</v>
+        <v>0.00762404426867768</v>
       </c>
       <c r="I38" t="n">
-        <v>6160.10829620345</v>
+        <v>4638.92552946671</v>
       </c>
       <c r="J38" t="n">
         <v>100</v>
       </c>
       <c r="K38" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L38" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B39" t="s">
         <v>35</v>
       </c>
       <c r="C39" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D39" t="n">
-        <v>-22143.852773775</v>
+        <v>-18252.5240091211</v>
       </c>
       <c r="E39" t="n">
-        <v>-22107.9480420228</v>
+        <v>-18216.6192773689</v>
       </c>
       <c r="F39" t="n">
-        <v>11077.9263868875</v>
+        <v>9132.26200456054</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0000344014647730964</v>
+        <v>0.000098229892928984</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00432531528279227</v>
+        <v>0.00764347504269286</v>
       </c>
       <c r="I39" t="n">
-        <v>5433.09434519175</v>
+        <v>4988.31407161228</v>
       </c>
       <c r="J39" t="n">
         <v>100</v>
       </c>
       <c r="K39" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L39" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40">
@@ -2609,7 +2630,7 @@
         <v>35</v>
       </c>
       <c r="C40" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D40" t="n">
         <v>-18465.0005679739</v>
@@ -2621,135 +2642,1731 @@
         <v>9238.50028398695</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0000986189190999559</v>
+        <v>0.000098467520676571</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00763692582301285</v>
+        <v>0.00763300985318857</v>
       </c>
       <c r="I40" t="n">
-        <v>4805.78512984572</v>
+        <v>3820.40803988208</v>
       </c>
       <c r="J40" t="n">
         <v>100</v>
       </c>
       <c r="K40" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L40" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B41" t="s">
         <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D41" t="n">
-        <v>-13301.5420123857</v>
+        <v>-17933.4795528587</v>
       </c>
       <c r="E41" t="n">
-        <v>-13265.6372806335</v>
+        <v>-17897.5748211065</v>
       </c>
       <c r="F41" t="n">
-        <v>6656.77100619286</v>
+        <v>8972.73977642934</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0011173770950026</v>
+        <v>0.0000984105151973771</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0242909732837304</v>
+        <v>0.00763773747391072</v>
       </c>
       <c r="I41" t="n">
-        <v>589.997045592963</v>
+        <v>4507.33045101984</v>
       </c>
       <c r="J41" t="n">
         <v>100</v>
       </c>
       <c r="K41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L41" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B42" t="s">
         <v>35</v>
       </c>
       <c r="C42" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D42" t="n">
-        <v>-16755.7121347858</v>
+        <v>-18844.8526666861</v>
       </c>
       <c r="E42" t="n">
-        <v>-16719.8074030336</v>
+        <v>-18814.9320568926</v>
       </c>
       <c r="F42" t="n">
-        <v>8383.85606739289</v>
+        <v>9427.42633334305</v>
       </c>
       <c r="G42" t="n">
-        <v>0.000357513516856228</v>
+        <v>0.0000811636279080973</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0133285270844448</v>
+        <v>0.00678531259707554</v>
       </c>
       <c r="I42" t="n">
-        <v>3166.08083140584</v>
+        <v>4959.39228703232</v>
       </c>
       <c r="J42" t="n">
         <v>100</v>
       </c>
       <c r="K42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L42" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" t="s">
+        <v>35</v>
+      </c>
+      <c r="C43" t="s">
+        <v>70</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-18969.8598262053</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-18933.9550944531</v>
+      </c>
+      <c r="F43" t="n">
+        <v>9490.92991310267</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.0000807664437590052</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.00678296027835998</v>
+      </c>
+      <c r="I43" t="n">
+        <v>5115.83761164808</v>
+      </c>
+      <c r="J43" t="n">
+        <v>100</v>
+      </c>
+      <c r="K43" t="s">
+        <v>45</v>
+      </c>
+      <c r="L43" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
         <v>34</v>
       </c>
-      <c r="B43" t="s">
-        <v>35</v>
-      </c>
-      <c r="C43" t="s">
+      <c r="B44" t="s">
+        <v>35</v>
+      </c>
+      <c r="C44" t="s">
+        <v>70</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-18979.930325161</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-18944.0255934088</v>
+      </c>
+      <c r="F44" t="n">
+        <v>9495.96516258049</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.0000806964530517839</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.00676496737106121</v>
+      </c>
+      <c r="I44" t="n">
+        <v>4744.40287206791</v>
+      </c>
+      <c r="J44" t="n">
+        <v>100</v>
+      </c>
+      <c r="K44" t="s">
+        <v>45</v>
+      </c>
+      <c r="L44" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" t="s">
+        <v>35</v>
+      </c>
+      <c r="C45" t="s">
+        <v>70</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-18445.4351106728</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-18409.5303789206</v>
+      </c>
+      <c r="F45" t="n">
+        <v>9228.7175553364</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.0000810523849618745</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.00679184805872536</v>
+      </c>
+      <c r="I45" t="n">
+        <v>4752.24052964361</v>
+      </c>
+      <c r="J45" t="n">
+        <v>100</v>
+      </c>
+      <c r="K45" t="s">
+        <v>45</v>
+      </c>
+      <c r="L45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" t="s">
+        <v>35</v>
+      </c>
+      <c r="C46" t="s">
+        <v>71</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-19007.3968106255</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-18977.476200832</v>
+      </c>
+      <c r="F46" t="n">
+        <v>9508.69840531277</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.0000751376498496025</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.00653815031518047</v>
+      </c>
+      <c r="I46" t="n">
+        <v>4984.53835442411</v>
+      </c>
+      <c r="J46" t="n">
+        <v>100</v>
+      </c>
+      <c r="K46" t="s">
+        <v>45</v>
+      </c>
+      <c r="L46" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" t="s">
+        <v>35</v>
+      </c>
+      <c r="C47" t="s">
+        <v>71</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-19117.2648737316</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-19081.3601419793</v>
+      </c>
+      <c r="F47" t="n">
+        <v>9564.63243686578</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.000075868779577224</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.00658502889222955</v>
+      </c>
+      <c r="I47" t="n">
+        <v>5182.22126184191</v>
+      </c>
+      <c r="J47" t="n">
+        <v>100</v>
+      </c>
+      <c r="K47" t="s">
+        <v>45</v>
+      </c>
+      <c r="L47" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>34</v>
+      </c>
+      <c r="B48" t="s">
+        <v>35</v>
+      </c>
+      <c r="C48" t="s">
+        <v>71</v>
+      </c>
+      <c r="D48" t="n">
+        <v>-19083.7648599836</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-19047.8601282314</v>
+      </c>
+      <c r="F48" t="n">
+        <v>9547.88242999181</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.0000751986899631813</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.00654719584457427</v>
+      </c>
+      <c r="I48" t="n">
+        <v>4273.22325038629</v>
+      </c>
+      <c r="J48" t="n">
+        <v>100</v>
+      </c>
+      <c r="K48" t="s">
+        <v>45</v>
+      </c>
+      <c r="L48" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49" t="s">
+        <v>71</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-19041.8639032016</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-19005.9591714494</v>
+      </c>
+      <c r="F49" t="n">
+        <v>9526.93195160081</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.0000756653608965852</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.00657653101702475</v>
+      </c>
+      <c r="I49" t="n">
+        <v>5000.4016191963</v>
+      </c>
+      <c r="J49" t="n">
+        <v>100</v>
+      </c>
+      <c r="K49" t="s">
+        <v>45</v>
+      </c>
+      <c r="L49" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" t="s">
+        <v>35</v>
+      </c>
+      <c r="C50" t="s">
+        <v>60</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-13207.8962469027</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-13177.9756371092</v>
+      </c>
+      <c r="F50" t="n">
+        <v>6608.94812345134</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.00111700386936028</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.024321574545893</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1051.6138570919</v>
+      </c>
+      <c r="J50" t="n">
+        <v>100</v>
+      </c>
+      <c r="K50" t="s">
+        <v>44</v>
+      </c>
+      <c r="L50" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" t="s">
+        <v>35</v>
+      </c>
+      <c r="C51" t="s">
         <v>61</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D51" t="n">
+        <v>-16688.7587376761</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-16658.8381278826</v>
+      </c>
+      <c r="F51" t="n">
+        <v>8349.37936883806</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.000358697849032201</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.0133369693265131</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2713.67013051358</v>
+      </c>
+      <c r="J51" t="n">
+        <v>100</v>
+      </c>
+      <c r="K51" t="s">
+        <v>44</v>
+      </c>
+      <c r="L51" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" t="s">
+        <v>35</v>
+      </c>
+      <c r="C52" t="s">
+        <v>62</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-19157.8116926813</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-19127.8910828878</v>
+      </c>
+      <c r="F52" t="n">
+        <v>9583.90584634064</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.000173111873391171</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.00874978208811587</v>
+      </c>
+      <c r="I52" t="n">
+        <v>3491.92893835333</v>
+      </c>
+      <c r="J52" t="n">
+        <v>100</v>
+      </c>
+      <c r="K52" t="s">
+        <v>44</v>
+      </c>
+      <c r="L52" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" t="s">
+        <v>35</v>
+      </c>
+      <c r="C53" t="s">
+        <v>64</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-18235.7141496069</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-18205.7935398134</v>
+      </c>
+      <c r="F53" t="n">
+        <v>9122.85707480347</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.000204620345555354</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.00923064946184809</v>
+      </c>
+      <c r="I53" t="n">
+        <v>4307.42738229818</v>
+      </c>
+      <c r="J53" t="n">
+        <v>100</v>
+      </c>
+      <c r="K53" t="s">
+        <v>44</v>
+      </c>
+      <c r="L53" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" t="s">
+        <v>35</v>
+      </c>
+      <c r="C54" t="s">
+        <v>65</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-14446.3970235722</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-14416.4764137787</v>
+      </c>
+      <c r="F54" t="n">
+        <v>7228.19851178609</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.000497755201730647</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.015878292761408</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2923.99885192463</v>
+      </c>
+      <c r="J54" t="n">
+        <v>100</v>
+      </c>
+      <c r="K54" t="s">
+        <v>44</v>
+      </c>
+      <c r="L54" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>36</v>
+      </c>
+      <c r="B55" t="s">
+        <v>35</v>
+      </c>
+      <c r="C55" t="s">
+        <v>66</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-21640.2971385716</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-21604.3924068193</v>
+      </c>
+      <c r="F55" t="n">
+        <v>10826.1485692858</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.0000223532175008213</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.00352284970559203</v>
+      </c>
+      <c r="I55" t="n">
+        <v>6201.41834791827</v>
+      </c>
+      <c r="J55" t="n">
+        <v>100</v>
+      </c>
+      <c r="K55" t="s">
+        <v>44</v>
+      </c>
+      <c r="L55" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>36</v>
+      </c>
+      <c r="B56" t="s">
+        <v>35</v>
+      </c>
+      <c r="C56" t="s">
+        <v>68</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-21775.2300244312</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-21739.325292679</v>
+      </c>
+      <c r="F56" t="n">
+        <v>10893.6150122156</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.0000344963526848082</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.00433578637453133</v>
+      </c>
+      <c r="I56" t="n">
+        <v>5737.89301323989</v>
+      </c>
+      <c r="J56" t="n">
+        <v>100</v>
+      </c>
+      <c r="K56" t="s">
+        <v>44</v>
+      </c>
+      <c r="L56" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>36</v>
+      </c>
+      <c r="B57" t="s">
+        <v>35</v>
+      </c>
+      <c r="C57" t="s">
+        <v>69</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-21710.3566868651</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-21674.4519551129</v>
+      </c>
+      <c r="F57" t="n">
+        <v>10861.1783434325</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.0000304993461572959</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.00408855784322493</v>
+      </c>
+      <c r="I57" t="n">
+        <v>5887.06846898562</v>
+      </c>
+      <c r="J57" t="n">
+        <v>100</v>
+      </c>
+      <c r="K57" t="s">
+        <v>44</v>
+      </c>
+      <c r="L57" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>36</v>
+      </c>
+      <c r="B58" t="s">
+        <v>35</v>
+      </c>
+      <c r="C58" t="s">
+        <v>70</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-18252.5240091211</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-18216.6192773689</v>
+      </c>
+      <c r="F58" t="n">
+        <v>9132.26200456054</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.0000997138709326372</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.00768966260579867</v>
+      </c>
+      <c r="I58" t="n">
+        <v>5020.223623959</v>
+      </c>
+      <c r="J58" t="n">
+        <v>100</v>
+      </c>
+      <c r="K58" t="s">
+        <v>44</v>
+      </c>
+      <c r="L58" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>36</v>
+      </c>
+      <c r="B59" t="s">
+        <v>35</v>
+      </c>
+      <c r="C59" t="s">
+        <v>71</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-18969.8598262053</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-18933.9550944531</v>
+      </c>
+      <c r="F59" t="n">
+        <v>9490.92991310267</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.0000812928951129839</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.00681279691536502</v>
+      </c>
+      <c r="I59" t="n">
+        <v>5145.01998269581</v>
+      </c>
+      <c r="J59" t="n">
+        <v>100</v>
+      </c>
+      <c r="K59" t="s">
+        <v>44</v>
+      </c>
+      <c r="L59" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>36</v>
+      </c>
+      <c r="B60" t="s">
+        <v>35</v>
+      </c>
+      <c r="C60" t="s">
+        <v>72</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-19117.2648737316</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-19081.3601419793</v>
+      </c>
+      <c r="F60" t="n">
+        <v>9564.63243686578</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.0000763994832086453</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.00663780427291206</v>
+      </c>
+      <c r="I60" t="n">
+        <v>5188.01710349232</v>
+      </c>
+      <c r="J60" t="n">
+        <v>100</v>
+      </c>
+      <c r="K60" t="s">
+        <v>44</v>
+      </c>
+      <c r="L60" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>36</v>
+      </c>
+      <c r="B61" t="s">
+        <v>35</v>
+      </c>
+      <c r="C61" t="s">
+        <v>60</v>
+      </c>
+      <c r="D61" t="n">
+        <v>-12886.6841895632</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-12850.779457811</v>
+      </c>
+      <c r="F61" t="n">
+        <v>6449.34209478161</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.00111998708288077</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.0243912623011049</v>
+      </c>
+      <c r="I61" t="n">
+        <v>2658.54110714379</v>
+      </c>
+      <c r="J61" t="n">
+        <v>100</v>
+      </c>
+      <c r="K61" t="s">
+        <v>44</v>
+      </c>
+      <c r="L61" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62" t="s">
+        <v>35</v>
+      </c>
+      <c r="C62" t="s">
+        <v>61</v>
+      </c>
+      <c r="D62" t="n">
+        <v>-16459.2335450459</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-16423.3288132937</v>
+      </c>
+      <c r="F62" t="n">
+        <v>8235.61677252294</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.000359553633729885</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.0134005293713835</v>
+      </c>
+      <c r="I62" t="n">
+        <v>3632.91127262384</v>
+      </c>
+      <c r="J62" t="n">
+        <v>100</v>
+      </c>
+      <c r="K62" t="s">
+        <v>44</v>
+      </c>
+      <c r="L62" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>36</v>
+      </c>
+      <c r="B63" t="s">
+        <v>35</v>
+      </c>
+      <c r="C63" t="s">
+        <v>62</v>
+      </c>
+      <c r="D63" t="n">
+        <v>-18960.5341690539</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-18924.6294373017</v>
+      </c>
+      <c r="F63" t="n">
+        <v>9486.26708452694</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.000173379545562513</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.00874464817762341</v>
+      </c>
+      <c r="I63" t="n">
+        <v>4469.83721075024</v>
+      </c>
+      <c r="J63" t="n">
+        <v>100</v>
+      </c>
+      <c r="K63" t="s">
+        <v>44</v>
+      </c>
+      <c r="L63" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>36</v>
+      </c>
+      <c r="B64" t="s">
+        <v>35</v>
+      </c>
+      <c r="C64" t="s">
+        <v>63</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-15123.4937397722</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-15087.58900802</v>
+      </c>
+      <c r="F64" t="n">
+        <v>7567.7468698861</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.000428298440333085</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.0149533648237795</v>
+      </c>
+      <c r="I64" t="n">
+        <v>3705.8767497545</v>
+      </c>
+      <c r="J64" t="n">
+        <v>100</v>
+      </c>
+      <c r="K64" t="s">
+        <v>44</v>
+      </c>
+      <c r="L64" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>36</v>
+      </c>
+      <c r="B65" t="s">
+        <v>35</v>
+      </c>
+      <c r="C65" t="s">
+        <v>64</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-18150.2559713468</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-18114.3512395946</v>
+      </c>
+      <c r="F65" t="n">
+        <v>9081.12798567339</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.000205489863478527</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.0092717928429477</v>
+      </c>
+      <c r="I65" t="n">
+        <v>4536.71715531798</v>
+      </c>
+      <c r="J65" t="n">
+        <v>100</v>
+      </c>
+      <c r="K65" t="s">
+        <v>44</v>
+      </c>
+      <c r="L65" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>36</v>
+      </c>
+      <c r="B66" t="s">
+        <v>35</v>
+      </c>
+      <c r="C66" t="s">
+        <v>65</v>
+      </c>
+      <c r="D66" t="n">
+        <v>-14264.3558075108</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-14228.4510757586</v>
+      </c>
+      <c r="F66" t="n">
+        <v>7138.17790375541</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.000499517062406974</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.0159105849633656</v>
+      </c>
+      <c r="I66" t="n">
+        <v>3667.09004176556</v>
+      </c>
+      <c r="J66" t="n">
+        <v>100</v>
+      </c>
+      <c r="K66" t="s">
+        <v>44</v>
+      </c>
+      <c r="L66" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>37</v>
+      </c>
+      <c r="B67" t="s">
+        <v>35</v>
+      </c>
+      <c r="C67" t="s">
+        <v>68</v>
+      </c>
+      <c r="D67" t="n">
+        <v>-21922.1562477529</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-21886.2515160007</v>
+      </c>
+      <c r="F67" t="n">
+        <v>10967.0781238764</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.0000345680721357787</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.00433773410563787</v>
+      </c>
+      <c r="I67" t="n">
+        <v>5811.5591325607</v>
+      </c>
+      <c r="J67" t="n">
+        <v>100</v>
+      </c>
+      <c r="K67" t="s">
+        <v>44</v>
+      </c>
+      <c r="L67" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>37</v>
+      </c>
+      <c r="B68" t="s">
+        <v>35</v>
+      </c>
+      <c r="C68" t="s">
+        <v>69</v>
+      </c>
+      <c r="D68" t="n">
+        <v>-22012.2166080391</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-21976.3118762869</v>
+      </c>
+      <c r="F68" t="n">
+        <v>11012.1083040196</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.0000307143365551819</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.00410291111855608</v>
+      </c>
+      <c r="I68" t="n">
+        <v>5832.10992128852</v>
+      </c>
+      <c r="J68" t="n">
+        <v>100</v>
+      </c>
+      <c r="K68" t="s">
+        <v>44</v>
+      </c>
+      <c r="L68" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>37</v>
+      </c>
+      <c r="B69" t="s">
+        <v>35</v>
+      </c>
+      <c r="C69" t="s">
+        <v>60</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-13272.5886735945</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-13236.6839418423</v>
+      </c>
+      <c r="F69" t="n">
+        <v>6642.29433679725</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.00111506312641247</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.0243114940550477</v>
+      </c>
+      <c r="I69" t="n">
+        <v>-954.938640688398</v>
+      </c>
+      <c r="J69" t="n">
+        <v>100</v>
+      </c>
+      <c r="K69" t="s">
+        <v>44</v>
+      </c>
+      <c r="L69" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>37</v>
+      </c>
+      <c r="B70" t="s">
+        <v>35</v>
+      </c>
+      <c r="C70" t="s">
+        <v>61</v>
+      </c>
+      <c r="D70" t="n">
+        <v>-16714.5673553433</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-16678.6626235911</v>
+      </c>
+      <c r="F70" t="n">
+        <v>8363.28367767167</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.000357907528885292</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.0133236556785465</v>
+      </c>
+      <c r="I70" t="n">
+        <v>3506.86690699592</v>
+      </c>
+      <c r="J70" t="n">
+        <v>100</v>
+      </c>
+      <c r="K70" t="s">
+        <v>44</v>
+      </c>
+      <c r="L70" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>37</v>
+      </c>
+      <c r="B71" t="s">
+        <v>35</v>
+      </c>
+      <c r="C71" t="s">
+        <v>62</v>
+      </c>
+      <c r="D71" t="n">
+        <v>-19180.8529014042</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-19144.948169652</v>
+      </c>
+      <c r="F71" t="n">
+        <v>9596.42645070209</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.000173312938629055</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.00874668437307545</v>
+      </c>
+      <c r="I71" t="n">
+        <v>4067.86518242951</v>
+      </c>
+      <c r="J71" t="n">
+        <v>100</v>
+      </c>
+      <c r="K71" t="s">
+        <v>44</v>
+      </c>
+      <c r="L71" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>37</v>
+      </c>
+      <c r="B72" t="s">
+        <v>35</v>
+      </c>
+      <c r="C72" t="s">
+        <v>63</v>
+      </c>
+      <c r="D72" t="n">
+        <v>-15518.5292120059</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-15482.6244802537</v>
+      </c>
+      <c r="F72" t="n">
+        <v>7765.26460600297</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.000428482527248528</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.0149318974829823</v>
+      </c>
+      <c r="I72" t="n">
+        <v>2857.45024859483</v>
+      </c>
+      <c r="J72" t="n">
+        <v>100</v>
+      </c>
+      <c r="K72" t="s">
+        <v>44</v>
+      </c>
+      <c r="L72" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>37</v>
+      </c>
+      <c r="B73" t="s">
+        <v>35</v>
+      </c>
+      <c r="C73" t="s">
+        <v>64</v>
+      </c>
+      <c r="D73" t="n">
+        <v>-18195.3717021399</v>
+      </c>
+      <c r="E73" t="n">
+        <v>-18159.4669703877</v>
+      </c>
+      <c r="F73" t="n">
+        <v>9103.68585106996</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.000205151988665101</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.00924562488450474</v>
+      </c>
+      <c r="I73" t="n">
+        <v>4510.56549898657</v>
+      </c>
+      <c r="J73" t="n">
+        <v>100</v>
+      </c>
+      <c r="K73" t="s">
+        <v>44</v>
+      </c>
+      <c r="L73" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>34</v>
+      </c>
+      <c r="B74" t="s">
+        <v>35</v>
+      </c>
+      <c r="C74" t="s">
+        <v>66</v>
+      </c>
+      <c r="D74" t="n">
+        <v>-21907.805785593</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-21871.9010538407</v>
+      </c>
+      <c r="F74" t="n">
+        <v>10959.9028927965</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.0000221909262070413</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.00350857180301007</v>
+      </c>
+      <c r="I74" t="n">
+        <v>5763.22817256436</v>
+      </c>
+      <c r="J74" t="n">
+        <v>100</v>
+      </c>
+      <c r="K74" t="s">
+        <v>44</v>
+      </c>
+      <c r="L74" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>34</v>
+      </c>
+      <c r="B75" t="s">
+        <v>35</v>
+      </c>
+      <c r="C75" t="s">
+        <v>68</v>
+      </c>
+      <c r="D75" t="n">
+        <v>-22143.852773775</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-22107.9480420228</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11077.9263868875</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.0000344412906441569</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.00432088171460377</v>
+      </c>
+      <c r="I75" t="n">
+        <v>5437.85940640172</v>
+      </c>
+      <c r="J75" t="n">
+        <v>100</v>
+      </c>
+      <c r="K75" t="s">
+        <v>44</v>
+      </c>
+      <c r="L75" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>34</v>
+      </c>
+      <c r="B76" t="s">
+        <v>35</v>
+      </c>
+      <c r="C76" t="s">
+        <v>69</v>
+      </c>
+      <c r="D76" t="n">
+        <v>-21895.756317562</v>
+      </c>
+      <c r="E76" t="n">
+        <v>-21859.8515858098</v>
+      </c>
+      <c r="F76" t="n">
+        <v>10953.878158781</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.0000306445255261147</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.00409466717270811</v>
+      </c>
+      <c r="I76" t="n">
+        <v>5129.20010934303</v>
+      </c>
+      <c r="J76" t="n">
+        <v>100</v>
+      </c>
+      <c r="K76" t="s">
+        <v>44</v>
+      </c>
+      <c r="L76" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>34</v>
+      </c>
+      <c r="B77" t="s">
+        <v>35</v>
+      </c>
+      <c r="C77" t="s">
+        <v>70</v>
+      </c>
+      <c r="D77" t="n">
+        <v>-18465.0005679739</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-18429.0958362217</v>
+      </c>
+      <c r="F77" t="n">
+        <v>9238.50028398695</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.0000976513819121709</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.00760844910085838</v>
+      </c>
+      <c r="I77" t="n">
+        <v>4651.52052010725</v>
+      </c>
+      <c r="J77" t="n">
+        <v>100</v>
+      </c>
+      <c r="K77" t="s">
+        <v>44</v>
+      </c>
+      <c r="L77" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>34</v>
+      </c>
+      <c r="B78" t="s">
+        <v>35</v>
+      </c>
+      <c r="C78" t="s">
+        <v>71</v>
+      </c>
+      <c r="D78" t="n">
+        <v>-18979.930325161</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-18944.0255934088</v>
+      </c>
+      <c r="F78" t="n">
+        <v>9495.96516258049</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.0000806524470839728</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.00678442336306669</v>
+      </c>
+      <c r="I78" t="n">
+        <v>4904.74801380754</v>
+      </c>
+      <c r="J78" t="n">
+        <v>100</v>
+      </c>
+      <c r="K78" t="s">
+        <v>44</v>
+      </c>
+      <c r="L78" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>34</v>
+      </c>
+      <c r="B79" t="s">
+        <v>35</v>
+      </c>
+      <c r="C79" t="s">
+        <v>72</v>
+      </c>
+      <c r="D79" t="n">
+        <v>-19083.7648599836</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-19047.8601282314</v>
+      </c>
+      <c r="F79" t="n">
+        <v>9547.88242999181</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.000075701964514223</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.00658479223177301</v>
+      </c>
+      <c r="I79" t="n">
+        <v>5059.14871156311</v>
+      </c>
+      <c r="J79" t="n">
+        <v>100</v>
+      </c>
+      <c r="K79" t="s">
+        <v>44</v>
+      </c>
+      <c r="L79" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>34</v>
+      </c>
+      <c r="B80" t="s">
+        <v>35</v>
+      </c>
+      <c r="C80" t="s">
+        <v>60</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-13301.5420123857</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-13265.6372806335</v>
+      </c>
+      <c r="F80" t="n">
+        <v>6656.77100619286</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.00111535198781881</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.0243461097605127</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1460.89282075391</v>
+      </c>
+      <c r="J80" t="n">
+        <v>100</v>
+      </c>
+      <c r="K80" t="s">
+        <v>44</v>
+      </c>
+      <c r="L80" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>34</v>
+      </c>
+      <c r="B81" t="s">
+        <v>35</v>
+      </c>
+      <c r="C81" t="s">
+        <v>61</v>
+      </c>
+      <c r="D81" t="n">
+        <v>-16755.7121347858</v>
+      </c>
+      <c r="E81" t="n">
+        <v>-16719.8074030336</v>
+      </c>
+      <c r="F81" t="n">
+        <v>8383.85606739289</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.000358311906816433</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.0133356319444019</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2738.55288217004</v>
+      </c>
+      <c r="J81" t="n">
+        <v>100</v>
+      </c>
+      <c r="K81" t="s">
+        <v>44</v>
+      </c>
+      <c r="L81" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>34</v>
+      </c>
+      <c r="B82" t="s">
+        <v>35</v>
+      </c>
+      <c r="C82" t="s">
+        <v>62</v>
+      </c>
+      <c r="D82" t="n">
+        <v>-19203.1063159103</v>
+      </c>
+      <c r="E82" t="n">
+        <v>-19167.2015841581</v>
+      </c>
+      <c r="F82" t="n">
+        <v>9607.55315795517</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.000173197985650938</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.00874048073550589</v>
+      </c>
+      <c r="I82" t="n">
+        <v>3164.23839893327</v>
+      </c>
+      <c r="J82" t="n">
+        <v>100</v>
+      </c>
+      <c r="K82" t="s">
+        <v>44</v>
+      </c>
+      <c r="L82" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>34</v>
+      </c>
+      <c r="B83" t="s">
+        <v>35</v>
+      </c>
+      <c r="C83" t="s">
+        <v>63</v>
+      </c>
+      <c r="D83" t="n">
+        <v>-15580.3567037644</v>
+      </c>
+      <c r="E83" t="n">
+        <v>-15544.4519720122</v>
+      </c>
+      <c r="F83" t="n">
+        <v>7796.17835188222</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.00042645367996808</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.0148824626149487</v>
+      </c>
+      <c r="I83" t="n">
+        <v>2990.1367093086</v>
+      </c>
+      <c r="J83" t="n">
+        <v>100</v>
+      </c>
+      <c r="K83" t="s">
+        <v>44</v>
+      </c>
+      <c r="L83" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>34</v>
+      </c>
+      <c r="B84" t="s">
+        <v>35</v>
+      </c>
+      <c r="C84" t="s">
+        <v>64</v>
+      </c>
+      <c r="D84" t="n">
+        <v>-18318.3939502536</v>
+      </c>
+      <c r="E84" t="n">
+        <v>-18282.4892185014</v>
+      </c>
+      <c r="F84" t="n">
+        <v>9165.19697512682</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.000203860081043165</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.00921797702585573</v>
+      </c>
+      <c r="I84" t="n">
+        <v>3448.12878340455</v>
+      </c>
+      <c r="J84" t="n">
+        <v>100</v>
+      </c>
+      <c r="K84" t="s">
+        <v>44</v>
+      </c>
+      <c r="L84" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>34</v>
+      </c>
+      <c r="B85" t="s">
+        <v>35</v>
+      </c>
+      <c r="C85" t="s">
+        <v>65</v>
+      </c>
+      <c r="D85" t="n">
         <v>-14556.4722711371</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E85" t="n">
         <v>-14520.5675393849</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F85" t="n">
         <v>7284.23613556855</v>
       </c>
-      <c r="G43" t="n">
-        <v>0.000498751522553309</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.0158513198728056</v>
-      </c>
-      <c r="I43" t="n">
-        <v>2727.78027539314</v>
-      </c>
-      <c r="J43" t="n">
-        <v>100</v>
-      </c>
-      <c r="K43" t="s">
+      <c r="G85" t="n">
+        <v>0.000498508651405117</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.0158785332225842</v>
+      </c>
+      <c r="I85" t="n">
+        <v>3007.31078665545</v>
+      </c>
+      <c r="J85" t="n">
+        <v>100</v>
+      </c>
+      <c r="K85" t="s">
         <v>44</v>
       </c>
-      <c r="L43" t="s">
+      <c r="L85" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2772,65 +4389,111 @@
         <v>19</v>
       </c>
       <c r="C1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E1" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F1" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G1" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
         <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.78125</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
         <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E3" t="n">
-        <v>0.84375</v>
+        <v>0.767578125</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>72</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" t="n">
+        <v>41</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.767578125</v>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2858,19 +4521,19 @@
         <v>42</v>
       </c>
       <c r="E1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F1" t="s">
         <v>43</v>
       </c>
       <c r="G1" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H1" t="s">
         <v>41</v>
       </c>
       <c r="I1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2">
@@ -2881,25 +4544,25 @@
         <v>44</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000672832847487877</v>
+        <v>0.000463318962272927</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000499902852630959</v>
+        <v>0.000359125741381043</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0180301772278061</v>
+        <v>0.0143250001109977</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0158976783975438</v>
+        <v>0.0133687493489483</v>
       </c>
       <c r="H2" t="n">
-        <v>-14777.6552725016</v>
+        <v>-16280.846750248</v>
       </c>
       <c r="I2" t="n">
-        <v>-14446.3970235722</v>
+        <v>-16573.996141361</v>
       </c>
     </row>
     <row r="3">
@@ -2910,83 +4573,83 @@
         <v>45</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000657732261677535</v>
+        <v>0.000400048945943705</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000498742008315416</v>
+        <v>0.000357558596297462</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0178438424627864</v>
+        <v>0.0128475292183633</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0158788667921911</v>
+        <v>0.0133197807246746</v>
       </c>
       <c r="H3" t="n">
-        <v>-14713.8267772652</v>
+        <v>-16933.8238800767</v>
       </c>
       <c r="I3" t="n">
-        <v>-14355.3764155415</v>
+        <v>-16701.6630465097</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
         <v>44</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0000494441411765139</v>
+        <v>0.0000536657221554166</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0000345216797439829</v>
+        <v>0.0000345322124102934</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00504260874953519</v>
+        <v>0.00531642059483129</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00432531528279227</v>
+        <v>0.0043367602400846</v>
       </c>
       <c r="H4" t="n">
-        <v>-20872.4095067455</v>
+        <v>-20562.5725746262</v>
       </c>
       <c r="I4" t="n">
-        <v>-21775.2300244312</v>
+        <v>-21675.3269127184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s">
         <v>45</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0000516863758482536</v>
+        <v>0.0000639709040906713</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0000344384977339093</v>
+        <v>0.0000754320254298833</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00516262538479136</v>
+        <v>0.00587869887305013</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0043307669738517</v>
+        <v>0.00656186343079951</v>
       </c>
       <c r="H5" t="n">
-        <v>-20611.2017348122</v>
+        <v>-19988.53383142</v>
       </c>
       <c r="I5" t="n">
-        <v>-21684.449904215</v>
+        <v>-19062.8143815926</v>
       </c>
     </row>
   </sheetData>
@@ -3005,10 +4668,10 @@
         <v>57</v>
       </c>
       <c r="B1" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D1" t="s">
         <v>48</v>
@@ -3019,41 +4682,55 @@
         <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
+        <v>28.5714285714286</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>33.3333333333333</v>
+        <v>71.4285714285714</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>66.6666666666667</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
